--- a/reports/service-tracking-report-JUNETTE-PONTILAR-evaluator-cache-serviceTracking-JUNETTE-PONTILAR-X-202501-202612.xlsx
+++ b/reports/service-tracking-report-JUNETTE-PONTILAR-evaluator-cache-serviceTracking-JUNETTE-PONTILAR-X-202501-202612.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -88,6 +88,24 @@
   </x:si>
   <x:si>
     <x:t>CHERYL MAY DELOSO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Retailer/Reseller Permit (RENEWAL)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TECHNOMART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>385 Jr Borja St. Aguinaldo, 32, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROX - MRR-10 - 04 - 326</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1429-808</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518180</x:t>
   </x:si>
   <x:si>
     <x:t>SUMMARY</x:t>
@@ -111,7 +129,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="14">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -180,7 +198,7 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -195,13 +213,6 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="14"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
@@ -438,7 +449,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="28">
+  <x:cellStyleXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -482,9 +493,6 @@
     <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -503,13 +511,10 @@
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -522,7 +527,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="30">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -574,6 +579,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -585,6 +594,10 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -609,15 +622,15 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1010,7 +1023,7 @@
       <x:c r="C8" s="15" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="15" t="s">
+      <x:c r="D8" s="16" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E8" s="15" t="s">
@@ -1022,84 +1035,118 @@
       <x:c r="G8" s="15" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="16">
+      <x:c r="H8" s="17">
         <x:v>46112.0874409838</x:v>
       </x:c>
-      <x:c r="I8" s="16">
+      <x:c r="I8" s="17">
         <x:v>46134</x:v>
       </x:c>
-      <x:c r="J8" s="15" t="s">
+      <x:c r="J8" s="16" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
+      <x:c r="K8" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L8" s="16">
+      <x:c r="L8" s="19">
         <x:v>46125.1598529398</x:v>
       </x:c>
       <x:c r="M8" s="15" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B9" s="9" t="s"/>
-      <x:c r="C9" s="9" t="s"/>
-      <x:c r="D9" s="9" t="s"/>
-      <x:c r="E9" s="9" t="s"/>
-      <x:c r="F9" s="9" t="s"/>
-      <x:c r="G9" s="9" t="s"/>
-      <x:c r="H9" s="9" t="s"/>
-      <x:c r="I9" s="9" t="s"/>
-      <x:c r="J9" s="9" t="s"/>
-      <x:c r="K9" s="9" t="s"/>
-      <x:c r="L9" s="9" t="s"/>
-      <x:c r="M9" s="9" t="s"/>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="15" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F9" s="15" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="G9" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H9" s="17">
+        <x:v>46126.2873086111</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>46130</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="K9" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L9" s="19">
+        <x:v>46127.0949605556</x:v>
+      </x:c>
+      <x:c r="M9" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="18" t="s">
+    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="20" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="22" t="s"/>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B13" s="23" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B14" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="26" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C11" s="19" t="s"/>
-      <x:c r="D11" s="19" t="s"/>
-      <x:c r="E11" s="20" t="s"/>
-      <x:c r="F11" s="20" t="s"/>
+      <x:c r="C15" s="27" t="s"/>
+      <x:c r="D15" s="27" t="s"/>
+      <x:c r="E15" s="27" t="s"/>
+      <x:c r="F15" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="21" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="23" t="s">
-        <x:v>24</x:v>
+    <x:row r="16" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B16" s="29" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C16" s="30" t="s"/>
+      <x:c r="D16" s="30" t="s"/>
+      <x:c r="E16" s="30" t="s"/>
+      <x:c r="F16" s="31" t="n">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="24" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="26" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="27" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2078,15 +2125,16 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="8">
+  <x:mergeCells count="9">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B11:F11"/>
-    <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B12:F12"/>
     <x:mergeCell ref="B13:E13"/>
     <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B16:E16"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-JUNETTE-PONTILAR-evaluator-cache-serviceTracking-JUNETTE-PONTILAR-X-202501-202612.xlsx
+++ b/reports/service-tracking-report-JUNETTE-PONTILAR-evaluator-cache-serviceTracking-JUNETTE-PONTILAR-X-202501-202612.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -69,12 +69,30 @@
     <x:t>Dealer Permit (RENEWAL)</x:t>
   </x:si>
   <x:si>
+    <x:t>INTERPACE CORPORATION</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WEST WING LKKS CENTER, Barangay LAPASAN, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14-REDP-CAG-01346</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1430-046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518191</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CHERYL MAY DELOSO</x:t>
+  </x:si>
+  <x:si>
     <x:t>SOLIDMARK WEST, INC.</x:t>
   </x:si>
   <x:si>
-    <x:t>REN</x:t>
-  </x:si>
-  <x:si>
     <x:t>MVVL3 K1 3RD FLOOR GAISANO CITY, Poblacion, City Of Valencia, Bukidnon</x:t>
   </x:si>
   <x:si>
@@ -87,12 +105,36 @@
     <x:t>1518169</x:t>
   </x:si>
   <x:si>
-    <x:t>CHERYL MAY DELOSO</x:t>
+    <x:t>UNIPACE CORPORATION</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CM RECTO AVE., CORRALES EXTN.,, Barangay 26, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14-REDP-CAG-01347</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1432-214</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518189</x:t>
   </x:si>
   <x:si>
     <x:t>Retailer/Reseller Permit (RENEWAL)</x:t>
   </x:si>
   <x:si>
+    <x:t>WEST WING LKKS CENTER, Barangay 31, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROX-MRR-10-07-135</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1428-833</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518192</x:t>
+  </x:si>
+  <x:si>
     <x:t>TECHNOMART</x:t>
   </x:si>
   <x:si>
@@ -106,6 +148,27 @@
   </x:si>
   <x:si>
     <x:t>1518180</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORTICH STREET, Barangay 04, City Of Malaybalay (Capital), Bukidnon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROX-MRR-13-06-152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1433-178</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518188</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROX-MRR-10-06-128</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1431-363</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518190</x:t>
   </x:si>
   <x:si>
     <x:t>SUMMARY</x:t>
@@ -1036,19 +1099,19 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="H8" s="17">
-        <x:v>46112.0874409838</x:v>
+        <x:v>46126.2900560185</x:v>
       </x:c>
       <x:c r="I8" s="17">
-        <x:v>46134</x:v>
+        <x:v>46162</x:v>
       </x:c>
       <x:c r="J8" s="16" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="K8" s="18" t="n">
-        <x:v>3030</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L8" s="19">
-        <x:v>46125.1598529398</x:v>
+        <x:v>46128.194732662</x:v>
       </x:c>
       <x:c r="M8" s="15" t="s">
         <x:v>21</x:v>
@@ -1056,102 +1119,287 @@
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
         <x:v>22</x:v>
-      </x:c>
-      <x:c r="C9" s="15" t="s">
-        <x:v>23</x:v>
       </x:c>
       <x:c r="D9" s="16" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E9" s="15" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F9" s="15" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="G9" s="15" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="H9" s="17">
+        <x:v>46112.0874409838</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>46134</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="s">
         <x:v>26</x:v>
-      </x:c>
-      <x:c r="H9" s="17">
-        <x:v>46126.2873086111</x:v>
-      </x:c>
-      <x:c r="I9" s="17">
-        <x:v>46130</x:v>
-      </x:c>
-      <x:c r="J9" s="16" t="s">
-        <x:v>27</x:v>
       </x:c>
       <x:c r="K9" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L9" s="19">
-        <x:v>46127.0949605556</x:v>
+        <x:v>46125.1598529398</x:v>
       </x:c>
       <x:c r="M9" s="15" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
+        <x:v>46126.3116678125</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>46196</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="K10" s="18" t="n">
+        <x:v>1950</x:v>
+      </x:c>
+      <x:c r="L10" s="19">
+        <x:v>46128.191368669</x:v>
+      </x:c>
+      <x:c r="M10" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
+        <x:v>46126.2721295949</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="K11" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L11" s="19">
+        <x:v>46128.1955625</x:v>
+      </x:c>
+      <x:c r="M11" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="20" t="s">
+      <x:c r="B12" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E12" s="15" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H12" s="17">
+        <x:v>46126.2873086111</x:v>
+      </x:c>
+      <x:c r="I12" s="17">
+        <x:v>46130</x:v>
+      </x:c>
+      <x:c r="J12" s="16" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K12" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L12" s="19">
+        <x:v>46127.0949605556</x:v>
+      </x:c>
+      <x:c r="M12" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D13" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E13" s="15" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F13" s="15" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G13" s="15" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H13" s="17">
+        <x:v>46126.3215783912</x:v>
+      </x:c>
+      <x:c r="I13" s="17">
+        <x:v>46198</x:v>
+      </x:c>
+      <x:c r="J13" s="16" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="K13" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L13" s="19">
+        <x:v>46128.1824279398</x:v>
+      </x:c>
+      <x:c r="M13" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B14" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C14" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D14" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E14" s="15" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="22" t="s"/>
+      <x:c r="F14" s="15" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="G14" s="15" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H14" s="17">
+        <x:v>46126.3072273495</x:v>
+      </x:c>
+      <x:c r="I14" s="17">
+        <x:v>46189</x:v>
+      </x:c>
+      <x:c r="J14" s="16" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="K14" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L14" s="19">
+        <x:v>46128.1930397685</x:v>
+      </x:c>
+      <x:c r="M14" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="23" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="s">
-        <x:v>30</x:v>
-      </x:c>
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B17" s="20" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C17" s="21" t="s"/>
+      <x:c r="D17" s="21" t="s"/>
+      <x:c r="E17" s="22" t="s"/>
+      <x:c r="F17" s="22" t="s"/>
     </x:row>
-    <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="26" t="s">
+    <x:row r="18" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B18" s="23" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C18" s="24" t="s"/>
+      <x:c r="D18" s="24" t="s"/>
+      <x:c r="E18" s="24" t="s"/>
+      <x:c r="F18" s="25" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B19" s="26" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
-        <x:v>1</x:v>
+      <x:c r="C19" s="27" t="s"/>
+      <x:c r="D19" s="27" t="s"/>
+      <x:c r="E19" s="27" t="s"/>
+      <x:c r="F19" s="28" t="n">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="26" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C15" s="27" t="s"/>
-      <x:c r="D15" s="27" t="s"/>
-      <x:c r="E15" s="27" t="s"/>
-      <x:c r="F15" s="28" t="n">
-        <x:v>1</x:v>
+    <x:row r="20" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B20" s="26" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C20" s="27" t="s"/>
+      <x:c r="D20" s="27" t="s"/>
+      <x:c r="E20" s="27" t="s"/>
+      <x:c r="F20" s="28" t="n">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="29" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C16" s="30" t="s"/>
-      <x:c r="D16" s="30" t="s"/>
-      <x:c r="E16" s="30" t="s"/>
-      <x:c r="F16" s="31" t="n">
-        <x:v>2</x:v>
+    <x:row r="21" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B21" s="29" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C21" s="30" t="s"/>
+      <x:c r="D21" s="30" t="s"/>
+      <x:c r="E21" s="30" t="s"/>
+      <x:c r="F21" s="31" t="n">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2130,11 +2378,11 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B12:F12"/>
-    <x:mergeCell ref="B13:E13"/>
-    <x:mergeCell ref="B14:E14"/>
-    <x:mergeCell ref="B15:E15"/>
-    <x:mergeCell ref="B16:E16"/>
+    <x:mergeCell ref="B17:F17"/>
+    <x:mergeCell ref="B18:E18"/>
+    <x:mergeCell ref="B19:E19"/>
+    <x:mergeCell ref="B20:E20"/>
+    <x:mergeCell ref="B21:E21"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-JUNETTE-PONTILAR-evaluator-cache-serviceTracking-JUNETTE-PONTILAR-X-202501-202612.xlsx
+++ b/reports/service-tracking-report-JUNETTE-PONTILAR-evaluator-cache-serviceTracking-JUNETTE-PONTILAR-X-202501-202612.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -69,12 +69,30 @@
     <x:t>Dealer Permit (RENEWAL)</x:t>
   </x:si>
   <x:si>
+    <x:t>EMCOR INCORPORATED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JVR BLDG J.R BORJA ST., BARANGAY 32, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">18-REDP-CAG-01365 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1434-610</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518195</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CHERYL MAY DELOSO</x:t>
+  </x:si>
+  <x:si>
     <x:t>INTERPACE CORPORATION</x:t>
   </x:si>
   <x:si>
-    <x:t>REN</x:t>
-  </x:si>
-  <x:si>
     <x:t>WEST WING LKKS CENTER, Barangay LAPASAN, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
   </x:si>
   <x:si>
@@ -85,9 +103,6 @@
   </x:si>
   <x:si>
     <x:t>1518191</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CHERYL MAY DELOSO</x:t>
   </x:si>
   <x:si>
     <x:t>SOLIDMARK WEST, INC.</x:t>
@@ -1099,10 +1114,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="H8" s="17">
-        <x:v>46126.2900560185</x:v>
+        <x:v>46128.1699027199</x:v>
       </x:c>
       <x:c r="I8" s="17">
-        <x:v>46162</x:v>
+        <x:v>46136</x:v>
       </x:c>
       <x:c r="J8" s="16" t="s">
         <x:v>20</x:v>
@@ -1111,7 +1126,7 @@
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L8" s="19">
-        <x:v>46128.194732662</x:v>
+        <x:v>46128.349008206</x:v>
       </x:c>
       <x:c r="M8" s="15" t="s">
         <x:v>21</x:v>
@@ -1137,19 +1152,19 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="H9" s="17">
-        <x:v>46112.0874409838</x:v>
+        <x:v>46126.2900560185</x:v>
       </x:c>
       <x:c r="I9" s="17">
-        <x:v>46134</x:v>
+        <x:v>46162</x:v>
       </x:c>
       <x:c r="J9" s="16" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="K9" s="18" t="n">
-        <x:v>3030</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L9" s="19">
-        <x:v>46125.1598529398</x:v>
+        <x:v>46128.194732662</x:v>
       </x:c>
       <x:c r="M9" s="15" t="s">
         <x:v>21</x:v>
@@ -1175,19 +1190,19 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="H10" s="17">
-        <x:v>46126.3116678125</x:v>
+        <x:v>46112.0874409838</x:v>
       </x:c>
       <x:c r="I10" s="17">
-        <x:v>46196</x:v>
+        <x:v>46134</x:v>
       </x:c>
       <x:c r="J10" s="16" t="s">
         <x:v>31</x:v>
       </x:c>
       <x:c r="K10" s="18" t="n">
-        <x:v>1950</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L10" s="19">
-        <x:v>46128.191368669</x:v>
+        <x:v>46125.1598529398</x:v>
       </x:c>
       <x:c r="M10" s="15" t="s">
         <x:v>21</x:v>
@@ -1195,10 +1210,10 @@
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="15" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="s">
-        <x:v>15</x:v>
       </x:c>
       <x:c r="D11" s="16" t="s">
         <x:v>16</x:v>
@@ -1213,19 +1228,19 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="H11" s="17">
-        <x:v>46126.2721295949</x:v>
+        <x:v>46126.3116678125</x:v>
       </x:c>
       <x:c r="I11" s="17">
-        <x:v>46224</x:v>
+        <x:v>46196</x:v>
       </x:c>
       <x:c r="J11" s="16" t="s">
         <x:v>36</x:v>
       </x:c>
       <x:c r="K11" s="18" t="n">
-        <x:v>3030</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L11" s="19">
-        <x:v>46128.1955625</x:v>
+        <x:v>46128.191368669</x:v>
       </x:c>
       <x:c r="M11" s="15" t="s">
         <x:v>21</x:v>
@@ -1233,10 +1248,10 @@
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="15" t="s">
-        <x:v>32</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C12" s="15" t="s">
-        <x:v>37</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D12" s="16" t="s">
         <x:v>16</x:v>
@@ -1251,10 +1266,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="H12" s="17">
-        <x:v>46126.2873086111</x:v>
+        <x:v>46126.2721295949</x:v>
       </x:c>
       <x:c r="I12" s="17">
-        <x:v>46130</x:v>
+        <x:v>46224</x:v>
       </x:c>
       <x:c r="J12" s="16" t="s">
         <x:v>41</x:v>
@@ -1263,7 +1278,7 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L12" s="19">
-        <x:v>46127.0949605556</x:v>
+        <x:v>46128.1955625</x:v>
       </x:c>
       <x:c r="M12" s="15" t="s">
         <x:v>21</x:v>
@@ -1271,37 +1286,37 @@
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="15" t="s">
-        <x:v>32</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C13" s="15" t="s">
-        <x:v>27</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D13" s="16" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E13" s="15" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F13" s="15" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="G13" s="15" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H13" s="17">
-        <x:v>46126.3215783912</x:v>
+        <x:v>46126.2873086111</x:v>
       </x:c>
       <x:c r="I13" s="17">
-        <x:v>46198</x:v>
+        <x:v>46130</x:v>
       </x:c>
       <x:c r="J13" s="16" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K13" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L13" s="19">
-        <x:v>46128.1824279398</x:v>
+        <x:v>46127.0949605556</x:v>
       </x:c>
       <x:c r="M13" s="15" t="s">
         <x:v>21</x:v>
@@ -1309,78 +1324,105 @@
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C14" s="15" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="C14" s="15" t="s">
-        <x:v>27</x:v>
       </x:c>
       <x:c r="D14" s="16" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E14" s="15" t="s">
-        <x:v>28</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F14" s="15" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G14" s="15" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H14" s="17">
-        <x:v>46126.3072273495</x:v>
+        <x:v>46126.3215783912</x:v>
       </x:c>
       <x:c r="I14" s="17">
-        <x:v>46189</x:v>
+        <x:v>46198</x:v>
       </x:c>
       <x:c r="J14" s="16" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="K14" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L14" s="19">
-        <x:v>46128.1930397685</x:v>
+        <x:v>46128.1824279398</x:v>
       </x:c>
       <x:c r="M14" s="15" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B15" s="15" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C15" s="15" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D15" s="16" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E15" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F15" s="15" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G15" s="15" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="H15" s="17">
+        <x:v>46126.3072273495</x:v>
+      </x:c>
+      <x:c r="I15" s="17">
+        <x:v>46189</x:v>
+      </x:c>
+      <x:c r="J15" s="16" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="K15" s="18" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L15" s="19">
+        <x:v>46128.1930397685</x:v>
+      </x:c>
+      <x:c r="M15" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="20" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C17" s="21" t="s"/>
-      <x:c r="D17" s="21" t="s"/>
-      <x:c r="E17" s="22" t="s"/>
-      <x:c r="F17" s="22" t="s"/>
+    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B18" s="20" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C18" s="21" t="s"/>
+      <x:c r="D18" s="21" t="s"/>
+      <x:c r="E18" s="22" t="s"/>
+      <x:c r="F18" s="22" t="s"/>
     </x:row>
-    <x:row r="18" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B18" s="23" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="s"/>
-      <x:c r="D18" s="24" t="s"/>
-      <x:c r="E18" s="24" t="s"/>
-      <x:c r="F18" s="25" t="s">
-        <x:v>51</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="26" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C19" s="27" t="s"/>
-      <x:c r="D19" s="27" t="s"/>
-      <x:c r="E19" s="27" t="s"/>
-      <x:c r="F19" s="28" t="n">
-        <x:v>3</x:v>
+    <x:row r="19" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B19" s="23" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C19" s="24" t="s"/>
+      <x:c r="D19" s="24" t="s"/>
+      <x:c r="E19" s="24" t="s"/>
+      <x:c r="F19" s="25" t="s">
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
       <x:c r="B20" s="26" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C20" s="27" t="s"/>
       <x:c r="D20" s="27" t="s"/>
@@ -1389,18 +1431,28 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B21" s="29" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C21" s="30" t="s"/>
-      <x:c r="D21" s="30" t="s"/>
-      <x:c r="E21" s="30" t="s"/>
-      <x:c r="F21" s="31" t="n">
-        <x:v>7</x:v>
+    <x:row r="21" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B21" s="26" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C21" s="27" t="s"/>
+      <x:c r="D21" s="27" t="s"/>
+      <x:c r="E21" s="27" t="s"/>
+      <x:c r="F21" s="28" t="n">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="22" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B22" s="29" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C22" s="30" t="s"/>
+      <x:c r="D22" s="30" t="s"/>
+      <x:c r="E22" s="30" t="s"/>
+      <x:c r="F22" s="31" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2378,11 +2430,11 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B17:F17"/>
-    <x:mergeCell ref="B18:E18"/>
+    <x:mergeCell ref="B18:F18"/>
     <x:mergeCell ref="B19:E19"/>
     <x:mergeCell ref="B20:E20"/>
     <x:mergeCell ref="B21:E21"/>
+    <x:mergeCell ref="B22:E22"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-JUNETTE-PONTILAR-evaluator-cache-serviceTracking-JUNETTE-PONTILAR-X-202501-202612.xlsx
+++ b/reports/service-tracking-report-JUNETTE-PONTILAR-evaluator-cache-serviceTracking-JUNETTE-PONTILAR-X-202501-202612.xlsx
@@ -207,7 +207,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -247,14 +247,6 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -527,7 +519,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -538,16 +530,13 @@
     <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -559,53 +548,53 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -640,87 +629,83 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1022,17 +1007,17 @@
       <x:c r="B5" s="12">
         <x:v>46113</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -1055,401 +1040,401 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>46128.1699027199</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>46136</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>46128.349008206</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>46126.2900560185</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>46162</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>46128.194732662</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="14" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>46112.0874409838</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>46134</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>46125.1598529398</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="D11" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="E11" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="16">
         <x:v>46126.3116678125</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="16">
         <x:v>46196</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="s">
+      <x:c r="J11" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="18">
         <x:v>46128.191368669</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="15" t="s">
+      <x:c r="B12" s="14" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="s">
+      <x:c r="C12" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="s">
+      <x:c r="D12" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E12" s="15" t="s">
+      <x:c r="E12" s="14" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="s">
+      <x:c r="F12" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="s">
+      <x:c r="G12" s="14" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="H12" s="17">
+      <x:c r="H12" s="16">
         <x:v>46126.2721295949</x:v>
       </x:c>
-      <x:c r="I12" s="17">
+      <x:c r="I12" s="16">
         <x:v>46224</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="s">
+      <x:c r="J12" s="15" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="K12" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L12" s="19">
+      <x:c r="L12" s="18">
         <x:v>46128.1955625</x:v>
       </x:c>
-      <x:c r="M12" s="15" t="s">
+      <x:c r="M12" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="15" t="s">
+      <x:c r="B13" s="14" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C13" s="15" t="s">
+      <x:c r="C13" s="14" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="s">
+      <x:c r="D13" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E13" s="15" t="s">
+      <x:c r="E13" s="14" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="s">
+      <x:c r="F13" s="14" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="s">
+      <x:c r="G13" s="14" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="H13" s="17">
+      <x:c r="H13" s="16">
         <x:v>46126.2873086111</x:v>
       </x:c>
-      <x:c r="I13" s="17">
+      <x:c r="I13" s="16">
         <x:v>46130</x:v>
       </x:c>
-      <x:c r="J13" s="16" t="s">
+      <x:c r="J13" s="15" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="K13" s="18" t="n">
+      <x:c r="K13" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L13" s="19">
+      <x:c r="L13" s="18">
         <x:v>46127.0949605556</x:v>
       </x:c>
-      <x:c r="M13" s="15" t="s">
+      <x:c r="M13" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="15" t="s">
+      <x:c r="B14" s="14" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C14" s="15" t="s">
+      <x:c r="C14" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="D14" s="16" t="s">
+      <x:c r="D14" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E14" s="15" t="s">
+      <x:c r="E14" s="14" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="F14" s="15" t="s">
+      <x:c r="F14" s="14" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="G14" s="15" t="s">
+      <x:c r="G14" s="14" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="H14" s="17">
+      <x:c r="H14" s="16">
         <x:v>46126.3215783912</x:v>
       </x:c>
-      <x:c r="I14" s="17">
+      <x:c r="I14" s="16">
         <x:v>46198</x:v>
       </x:c>
-      <x:c r="J14" s="16" t="s">
+      <x:c r="J14" s="15" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="K14" s="18" t="n">
+      <x:c r="K14" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L14" s="19">
+      <x:c r="L14" s="18">
         <x:v>46128.1824279398</x:v>
       </x:c>
-      <x:c r="M14" s="15" t="s">
+      <x:c r="M14" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="15" t="s">
+      <x:c r="B15" s="14" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C15" s="15" t="s">
+      <x:c r="C15" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="D15" s="16" t="s">
+      <x:c r="D15" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E15" s="15" t="s">
+      <x:c r="E15" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="F15" s="15" t="s">
+      <x:c r="F15" s="14" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="G15" s="15" t="s">
+      <x:c r="G15" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="H15" s="17">
+      <x:c r="H15" s="16">
         <x:v>46126.3072273495</x:v>
       </x:c>
-      <x:c r="I15" s="17">
+      <x:c r="I15" s="16">
         <x:v>46189</x:v>
       </x:c>
-      <x:c r="J15" s="16" t="s">
+      <x:c r="J15" s="15" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="K15" s="18" t="n">
+      <x:c r="K15" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L15" s="19">
+      <x:c r="L15" s="18">
         <x:v>46128.1930397685</x:v>
       </x:c>
-      <x:c r="M15" s="15" t="s">
+      <x:c r="M15" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="20" t="s">
+      <x:c r="B18" s="19" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="C18" s="21" t="s"/>
-      <x:c r="D18" s="21" t="s"/>
-      <x:c r="E18" s="22" t="s"/>
-      <x:c r="F18" s="22" t="s"/>
+      <x:c r="C18" s="20" t="s"/>
+      <x:c r="D18" s="20" t="s"/>
+      <x:c r="E18" s="21" t="s"/>
+      <x:c r="F18" s="21" t="s"/>
     </x:row>
     <x:row r="19" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B19" s="23" t="s">
+      <x:c r="B19" s="22" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="C19" s="24" t="s"/>
-      <x:c r="D19" s="24" t="s"/>
-      <x:c r="E19" s="24" t="s"/>
-      <x:c r="F19" s="25" t="s">
+      <x:c r="C19" s="23" t="s"/>
+      <x:c r="D19" s="23" t="s"/>
+      <x:c r="E19" s="23" t="s"/>
+      <x:c r="F19" s="24" t="s">
         <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="26" t="s">
+      <x:c r="B20" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C20" s="27" t="s"/>
-      <x:c r="D20" s="27" t="s"/>
-      <x:c r="E20" s="27" t="s"/>
-      <x:c r="F20" s="28" t="n">
+      <x:c r="C20" s="26" t="s"/>
+      <x:c r="D20" s="26" t="s"/>
+      <x:c r="E20" s="26" t="s"/>
+      <x:c r="F20" s="27" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="26" t="s">
+      <x:c r="B21" s="25" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C21" s="27" t="s"/>
-      <x:c r="D21" s="27" t="s"/>
-      <x:c r="E21" s="27" t="s"/>
-      <x:c r="F21" s="28" t="n">
+      <x:c r="C21" s="26" t="s"/>
+      <x:c r="D21" s="26" t="s"/>
+      <x:c r="E21" s="26" t="s"/>
+      <x:c r="F21" s="27" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B22" s="29" t="s">
+      <x:c r="B22" s="28" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="C22" s="30" t="s"/>
-      <x:c r="D22" s="30" t="s"/>
-      <x:c r="E22" s="30" t="s"/>
-      <x:c r="F22" s="31" t="n">
+      <x:c r="C22" s="29" t="s"/>
+      <x:c r="D22" s="29" t="s"/>
+      <x:c r="E22" s="29" t="s"/>
+      <x:c r="F22" s="30" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-JUNETTE-PONTILAR-evaluator-cache-serviceTracking-JUNETTE-PONTILAR-X-202501-202612.xlsx
+++ b/reports/service-tracking-report-JUNETTE-PONTILAR-evaluator-cache-serviceTracking-JUNETTE-PONTILAR-X-202501-202612.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -69,12 +69,30 @@
     <x:t>Dealer Permit (RENEWAL)</x:t>
   </x:si>
   <x:si>
+    <x:t>EMCOR INC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P-3 NATIONAL HIGHWAY, POBLACION, Alubijid, Misamis Oriental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18-REDP-CAG-01362</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1444-814</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518210 A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CHERYL MAY DELOSO</x:t>
+  </x:si>
+  <x:si>
     <x:t>EMCOR INCORPORATED</x:t>
   </x:si>
   <x:si>
-    <x:t>REN</x:t>
-  </x:si>
-  <x:si>
     <x:t>JVR BLDG J.R BORJA ST., BARANGAY 32, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
   </x:si>
   <x:si>
@@ -85,9 +103,6 @@
   </x:si>
   <x:si>
     <x:t>1518195</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CHERYL MAY DELOSO</x:t>
   </x:si>
   <x:si>
     <x:t>INTERPACE CORPORATION</x:t>
@@ -1099,10 +1114,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="H8" s="16">
-        <x:v>46128.1699027199</x:v>
+        <x:v>46132.2785644329</x:v>
       </x:c>
       <x:c r="I8" s="16">
-        <x:v>46136</x:v>
+        <x:v>46135</x:v>
       </x:c>
       <x:c r="J8" s="15" t="s">
         <x:v>20</x:v>
@@ -1111,7 +1126,7 @@
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L8" s="18">
-        <x:v>46128.349008206</x:v>
+        <x:v>46133.1152077083</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
@@ -1137,10 +1152,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="H9" s="16">
-        <x:v>46126.2900560185</x:v>
+        <x:v>46128.1699027199</x:v>
       </x:c>
       <x:c r="I9" s="16">
-        <x:v>46162</x:v>
+        <x:v>46136</x:v>
       </x:c>
       <x:c r="J9" s="15" t="s">
         <x:v>26</x:v>
@@ -1149,7 +1164,7 @@
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L9" s="18">
-        <x:v>46128.194732662</x:v>
+        <x:v>46128.349008206</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
@@ -1175,19 +1190,19 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="H10" s="16">
-        <x:v>46112.0874409838</x:v>
+        <x:v>46126.2900560185</x:v>
       </x:c>
       <x:c r="I10" s="16">
-        <x:v>46134</x:v>
+        <x:v>46162</x:v>
       </x:c>
       <x:c r="J10" s="15" t="s">
         <x:v>31</x:v>
       </x:c>
       <x:c r="K10" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L10" s="18">
-        <x:v>46125.1598529398</x:v>
+        <x:v>46128.194732662</x:v>
       </x:c>
       <x:c r="M10" s="14" t="s">
         <x:v>21</x:v>
@@ -1213,19 +1228,19 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="H11" s="16">
-        <x:v>46126.3116678125</x:v>
+        <x:v>46112.0874409838</x:v>
       </x:c>
       <x:c r="I11" s="16">
-        <x:v>46196</x:v>
+        <x:v>46134</x:v>
       </x:c>
       <x:c r="J11" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
       <x:c r="K11" s="17" t="n">
-        <x:v>1950</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L11" s="18">
-        <x:v>46128.191368669</x:v>
+        <x:v>46125.1598529398</x:v>
       </x:c>
       <x:c r="M11" s="14" t="s">
         <x:v>21</x:v>
@@ -1233,10 +1248,10 @@
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="14" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="s">
         <x:v>37</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
-        <x:v>22</x:v>
       </x:c>
       <x:c r="D12" s="15" t="s">
         <x:v>16</x:v>
@@ -1251,19 +1266,19 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="H12" s="16">
-        <x:v>46126.2721295949</x:v>
+        <x:v>46126.3116678125</x:v>
       </x:c>
       <x:c r="I12" s="16">
-        <x:v>46224</x:v>
+        <x:v>46196</x:v>
       </x:c>
       <x:c r="J12" s="15" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="K12" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L12" s="18">
-        <x:v>46128.1955625</x:v>
+        <x:v>46128.191368669</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
         <x:v>21</x:v>
@@ -1271,10 +1286,10 @@
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="14" t="s">
-        <x:v>37</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C13" s="14" t="s">
-        <x:v>42</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D13" s="15" t="s">
         <x:v>16</x:v>
@@ -1289,10 +1304,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="H13" s="16">
-        <x:v>46126.2873086111</x:v>
+        <x:v>46126.2721295949</x:v>
       </x:c>
       <x:c r="I13" s="16">
-        <x:v>46130</x:v>
+        <x:v>46224</x:v>
       </x:c>
       <x:c r="J13" s="15" t="s">
         <x:v>46</x:v>
@@ -1301,7 +1316,7 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L13" s="18">
-        <x:v>46127.0949605556</x:v>
+        <x:v>46128.1955625</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
         <x:v>21</x:v>
@@ -1309,37 +1324,37 @@
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="14" t="s">
-        <x:v>37</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C14" s="14" t="s">
-        <x:v>32</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D14" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E14" s="14" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F14" s="14" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G14" s="14" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H14" s="16">
-        <x:v>46126.3215783912</x:v>
+        <x:v>46126.2873086111</x:v>
       </x:c>
       <x:c r="I14" s="16">
-        <x:v>46198</x:v>
+        <x:v>46130</x:v>
       </x:c>
       <x:c r="J14" s="15" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K14" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L14" s="18">
-        <x:v>46128.1824279398</x:v>
+        <x:v>46127.0949605556</x:v>
       </x:c>
       <x:c r="M14" s="14" t="s">
         <x:v>21</x:v>
@@ -1347,98 +1362,135 @@
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="14" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="s">
         <x:v>37</x:v>
-      </x:c>
-      <x:c r="C15" s="14" t="s">
-        <x:v>32</x:v>
       </x:c>
       <x:c r="D15" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E15" s="14" t="s">
-        <x:v>33</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F15" s="14" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G15" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H15" s="16">
-        <x:v>46126.3072273495</x:v>
+        <x:v>46126.3215783912</x:v>
       </x:c>
       <x:c r="I15" s="16">
-        <x:v>46189</x:v>
+        <x:v>46198</x:v>
       </x:c>
       <x:c r="J15" s="15" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="K15" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L15" s="18">
-        <x:v>46128.1930397685</x:v>
+        <x:v>46128.1824279398</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B16" s="14" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C16" s="14" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E16" s="14" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="G16" s="14" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H16" s="16">
+        <x:v>46126.3072273495</x:v>
+      </x:c>
+      <x:c r="I16" s="16">
+        <x:v>46189</x:v>
+      </x:c>
+      <x:c r="J16" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="K16" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L16" s="18">
+        <x:v>46128.1930397685</x:v>
+      </x:c>
+      <x:c r="M16" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="19" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C18" s="20" t="s"/>
-      <x:c r="D18" s="20" t="s"/>
-      <x:c r="E18" s="21" t="s"/>
-      <x:c r="F18" s="21" t="s"/>
+    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B19" s="19" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C19" s="20" t="s"/>
+      <x:c r="D19" s="20" t="s"/>
+      <x:c r="E19" s="21" t="s"/>
+      <x:c r="F19" s="21" t="s"/>
     </x:row>
-    <x:row r="19" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B19" s="22" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C19" s="23" t="s"/>
-      <x:c r="D19" s="23" t="s"/>
-      <x:c r="E19" s="23" t="s"/>
-      <x:c r="F19" s="24" t="s">
-        <x:v>56</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="25" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C20" s="26" t="s"/>
-      <x:c r="D20" s="26" t="s"/>
-      <x:c r="E20" s="26" t="s"/>
-      <x:c r="F20" s="27" t="n">
-        <x:v>4</x:v>
+    <x:row r="20" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B20" s="22" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C20" s="23" t="s"/>
+      <x:c r="D20" s="23" t="s"/>
+      <x:c r="E20" s="23" t="s"/>
+      <x:c r="F20" s="24" t="s">
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
       <x:c r="B21" s="25" t="s">
-        <x:v>37</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C21" s="26" t="s"/>
       <x:c r="D21" s="26" t="s"/>
       <x:c r="E21" s="26" t="s"/>
       <x:c r="F21" s="27" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B22" s="25" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C22" s="26" t="s"/>
+      <x:c r="D22" s="26" t="s"/>
+      <x:c r="E22" s="26" t="s"/>
+      <x:c r="F22" s="27" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B22" s="28" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C22" s="29" t="s"/>
-      <x:c r="D22" s="29" t="s"/>
-      <x:c r="E22" s="29" t="s"/>
-      <x:c r="F22" s="30" t="n">
-        <x:v>8</x:v>
+    <x:row r="23" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B23" s="28" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C23" s="29" t="s"/>
+      <x:c r="D23" s="29" t="s"/>
+      <x:c r="E23" s="29" t="s"/>
+      <x:c r="F23" s="30" t="n">
+        <x:v>9</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2415,11 +2467,11 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B18:F18"/>
-    <x:mergeCell ref="B19:E19"/>
+    <x:mergeCell ref="B19:F19"/>
     <x:mergeCell ref="B20:E20"/>
     <x:mergeCell ref="B21:E21"/>
     <x:mergeCell ref="B22:E22"/>
+    <x:mergeCell ref="B23:E23"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-JUNETTE-PONTILAR-evaluator-cache-serviceTracking-JUNETTE-PONTILAR-X-202501-202612.xlsx
+++ b/reports/service-tracking-report-JUNETTE-PONTILAR-evaluator-cache-serviceTracking-JUNETTE-PONTILAR-X-202501-202612.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -103,6 +103,21 @@
   </x:si>
   <x:si>
     <x:t>1518195</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMCOR, INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hannah Shangrila Bldg. Zone 1B, Iponan, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19-REDP-CAG-01364</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1448-935</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518223 A</x:t>
   </x:si>
   <x:si>
     <x:t>INTERPACE CORPORATION</x:t>
@@ -1190,10 +1205,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="H10" s="16">
-        <x:v>46126.2900560185</x:v>
+        <x:v>46133.2374101505</x:v>
       </x:c>
       <x:c r="I10" s="16">
-        <x:v>46162</x:v>
+        <x:v>46135</x:v>
       </x:c>
       <x:c r="J10" s="15" t="s">
         <x:v>31</x:v>
@@ -1202,7 +1217,7 @@
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L10" s="18">
-        <x:v>46128.194732662</x:v>
+        <x:v>46134.0815209838</x:v>
       </x:c>
       <x:c r="M10" s="14" t="s">
         <x:v>21</x:v>
@@ -1228,19 +1243,19 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="H11" s="16">
-        <x:v>46112.0874409838</x:v>
+        <x:v>46126.2900560185</x:v>
       </x:c>
       <x:c r="I11" s="16">
-        <x:v>46134</x:v>
+        <x:v>46162</x:v>
       </x:c>
       <x:c r="J11" s="15" t="s">
         <x:v>36</x:v>
       </x:c>
       <x:c r="K11" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L11" s="18">
-        <x:v>46125.1598529398</x:v>
+        <x:v>46128.194732662</x:v>
       </x:c>
       <x:c r="M11" s="14" t="s">
         <x:v>21</x:v>
@@ -1266,19 +1281,19 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="H12" s="16">
-        <x:v>46126.3116678125</x:v>
+        <x:v>46112.0874409838</x:v>
       </x:c>
       <x:c r="I12" s="16">
-        <x:v>46196</x:v>
+        <x:v>46134</x:v>
       </x:c>
       <x:c r="J12" s="15" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="K12" s="17" t="n">
-        <x:v>1950</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L12" s="18">
-        <x:v>46128.191368669</x:v>
+        <x:v>46125.1598529398</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
         <x:v>21</x:v>
@@ -1286,10 +1301,10 @@
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="14" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="C13" s="14" t="s">
-        <x:v>27</x:v>
       </x:c>
       <x:c r="D13" s="15" t="s">
         <x:v>16</x:v>
@@ -1304,19 +1319,19 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="H13" s="16">
-        <x:v>46126.2721295949</x:v>
+        <x:v>46126.3116678125</x:v>
       </x:c>
       <x:c r="I13" s="16">
-        <x:v>46224</x:v>
+        <x:v>46196</x:v>
       </x:c>
       <x:c r="J13" s="15" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="K13" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L13" s="18">
-        <x:v>46128.1955625</x:v>
+        <x:v>46128.191368669</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
         <x:v>21</x:v>
@@ -1324,10 +1339,10 @@
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="14" t="s">
-        <x:v>42</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C14" s="14" t="s">
-        <x:v>47</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D14" s="15" t="s">
         <x:v>16</x:v>
@@ -1342,10 +1357,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="H14" s="16">
-        <x:v>46126.2873086111</x:v>
+        <x:v>46126.2721295949</x:v>
       </x:c>
       <x:c r="I14" s="16">
-        <x:v>46130</x:v>
+        <x:v>46224</x:v>
       </x:c>
       <x:c r="J14" s="15" t="s">
         <x:v>51</x:v>
@@ -1354,7 +1369,7 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L14" s="18">
-        <x:v>46127.0949605556</x:v>
+        <x:v>46128.1955625</x:v>
       </x:c>
       <x:c r="M14" s="14" t="s">
         <x:v>21</x:v>
@@ -1362,37 +1377,37 @@
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="14" t="s">
-        <x:v>42</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C15" s="14" t="s">
-        <x:v>37</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D15" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E15" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F15" s="14" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G15" s="14" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H15" s="16">
-        <x:v>46126.3215783912</x:v>
+        <x:v>46126.2873086111</x:v>
       </x:c>
       <x:c r="I15" s="16">
-        <x:v>46198</x:v>
+        <x:v>46130</x:v>
       </x:c>
       <x:c r="J15" s="15" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="K15" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L15" s="18">
-        <x:v>46128.1824279398</x:v>
+        <x:v>46127.0949605556</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
         <x:v>21</x:v>
@@ -1400,98 +1415,135 @@
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="14" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C16" s="14" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="C16" s="14" t="s">
-        <x:v>37</x:v>
       </x:c>
       <x:c r="D16" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E16" s="14" t="s">
-        <x:v>38</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F16" s="14" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G16" s="14" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H16" s="16">
-        <x:v>46126.3072273495</x:v>
+        <x:v>46126.3215783912</x:v>
       </x:c>
       <x:c r="I16" s="16">
-        <x:v>46189</x:v>
+        <x:v>46198</x:v>
       </x:c>
       <x:c r="J16" s="15" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="K16" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L16" s="18">
-        <x:v>46128.1930397685</x:v>
+        <x:v>46128.1824279398</x:v>
       </x:c>
       <x:c r="M16" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B17" s="14" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C17" s="14" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E17" s="14" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="G17" s="14" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="H17" s="16">
+        <x:v>46126.3072273495</x:v>
+      </x:c>
+      <x:c r="I17" s="16">
+        <x:v>46189</x:v>
+      </x:c>
+      <x:c r="J17" s="15" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="K17" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L17" s="18">
+        <x:v>46128.1930397685</x:v>
+      </x:c>
+      <x:c r="M17" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="19" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B19" s="19" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C19" s="20" t="s"/>
-      <x:c r="D19" s="20" t="s"/>
-      <x:c r="E19" s="21" t="s"/>
-      <x:c r="F19" s="21" t="s"/>
+    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B20" s="19" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C20" s="20" t="s"/>
+      <x:c r="D20" s="20" t="s"/>
+      <x:c r="E20" s="21" t="s"/>
+      <x:c r="F20" s="21" t="s"/>
     </x:row>
-    <x:row r="20" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B20" s="22" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C20" s="23" t="s"/>
-      <x:c r="D20" s="23" t="s"/>
-      <x:c r="E20" s="23" t="s"/>
-      <x:c r="F20" s="24" t="s">
-        <x:v>61</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="25" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C21" s="26" t="s"/>
-      <x:c r="D21" s="26" t="s"/>
-      <x:c r="E21" s="26" t="s"/>
-      <x:c r="F21" s="27" t="n">
-        <x:v>5</x:v>
+    <x:row r="21" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B21" s="22" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C21" s="23" t="s"/>
+      <x:c r="D21" s="23" t="s"/>
+      <x:c r="E21" s="23" t="s"/>
+      <x:c r="F21" s="24" t="s">
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
       <x:c r="B22" s="25" t="s">
-        <x:v>42</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C22" s="26" t="s"/>
       <x:c r="D22" s="26" t="s"/>
       <x:c r="E22" s="26" t="s"/>
       <x:c r="F22" s="27" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B23" s="25" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C23" s="26" t="s"/>
+      <x:c r="D23" s="26" t="s"/>
+      <x:c r="E23" s="26" t="s"/>
+      <x:c r="F23" s="27" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B23" s="28" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C23" s="29" t="s"/>
-      <x:c r="D23" s="29" t="s"/>
-      <x:c r="E23" s="29" t="s"/>
-      <x:c r="F23" s="30" t="n">
-        <x:v>9</x:v>
+    <x:row r="24" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B24" s="28" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C24" s="29" t="s"/>
+      <x:c r="D24" s="29" t="s"/>
+      <x:c r="E24" s="29" t="s"/>
+      <x:c r="F24" s="30" t="n">
+        <x:v>10</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2467,11 +2519,11 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B19:F19"/>
-    <x:mergeCell ref="B20:E20"/>
+    <x:mergeCell ref="B20:F20"/>
     <x:mergeCell ref="B21:E21"/>
     <x:mergeCell ref="B22:E22"/>
     <x:mergeCell ref="B23:E23"/>
+    <x:mergeCell ref="B24:E24"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-JUNETTE-PONTILAR-evaluator-cache-serviceTracking-JUNETTE-PONTILAR-X-202501-202612.xlsx
+++ b/reports/service-tracking-report-JUNETTE-PONTILAR-evaluator-cache-serviceTracking-JUNETTE-PONTILAR-X-202501-202612.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -90,6 +90,18 @@
     <x:t>CHERYL MAY DELOSO</x:t>
   </x:si>
   <x:si>
+    <x:t>NADAL BDLG NATIONAL HIGHWAY, BARANGAY 3, Gingoog City, Misamis Oriental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18-REDP-CAG-01361</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1436-764</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518230 A</x:t>
+  </x:si>
+  <x:si>
     <x:t>EMCOR INCORPORATED</x:t>
   </x:si>
   <x:si>
@@ -178,6 +190,21 @@
   </x:si>
   <x:si>
     <x:t>1518192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOLIDMARK WEST, INC. - ROBINSONS VALENCIA SES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Robinson's Place, Bagontaas, City Of Valencia, Bukidnon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROX-MRR-18-12-410</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1424-309</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518227 A</x:t>
   </x:si>
   <x:si>
     <x:t>TECHNOMART</x:t>
@@ -1152,34 +1179,34 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>22</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D9" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="G9" s="14" t="s">
+      <x:c r="H9" s="16">
+        <x:v>46128.2089466088</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
+        <x:v>46135</x:v>
+      </x:c>
+      <x:c r="J9" s="15" t="s">
         <x:v>25</x:v>
-      </x:c>
-      <x:c r="H9" s="16">
-        <x:v>46128.1699027199</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
-        <x:v>46136</x:v>
-      </x:c>
-      <x:c r="J9" s="15" t="s">
-        <x:v>26</x:v>
       </x:c>
       <x:c r="K9" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L9" s="18">
-        <x:v>46128.349008206</x:v>
+        <x:v>46134.3002672917</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
@@ -1190,34 +1217,34 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C10" s="14" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D10" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E10" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="F10" s="14" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="s">
+      <x:c r="H10" s="16">
+        <x:v>46128.1699027199</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
+        <x:v>46136</x:v>
+      </x:c>
+      <x:c r="J10" s="15" t="s">
         <x:v>30</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
-        <x:v>46133.2374101505</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>46135</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="s">
-        <x:v>31</x:v>
       </x:c>
       <x:c r="K10" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L10" s="18">
-        <x:v>46134.0815209838</x:v>
+        <x:v>46128.349008206</x:v>
       </x:c>
       <x:c r="M10" s="14" t="s">
         <x:v>21</x:v>
@@ -1228,34 +1255,34 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C11" s="14" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D11" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E11" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="F11" s="14" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="G11" s="14" t="s">
+      <x:c r="H11" s="16">
+        <x:v>46133.2374101505</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
+        <x:v>46135</x:v>
+      </x:c>
+      <x:c r="J11" s="15" t="s">
         <x:v>35</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>46126.2900560185</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>46162</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="s">
-        <x:v>36</x:v>
       </x:c>
       <x:c r="K11" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L11" s="18">
-        <x:v>46128.194732662</x:v>
+        <x:v>46134.0815209838</x:v>
       </x:c>
       <x:c r="M11" s="14" t="s">
         <x:v>21</x:v>
@@ -1266,34 +1293,34 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C12" s="14" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D12" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E12" s="14" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F12" s="14" t="s">
+      <x:c r="G12" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="G12" s="14" t="s">
+      <x:c r="H12" s="16">
+        <x:v>46126.2900560185</x:v>
+      </x:c>
+      <x:c r="I12" s="16">
+        <x:v>46162</x:v>
+      </x:c>
+      <x:c r="J12" s="15" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="H12" s="16">
-        <x:v>46112.0874409838</x:v>
-      </x:c>
-      <x:c r="I12" s="16">
-        <x:v>46134</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="s">
-        <x:v>41</x:v>
-      </x:c>
       <x:c r="K12" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L12" s="18">
-        <x:v>46125.1598529398</x:v>
+        <x:v>46128.194732662</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
         <x:v>21</x:v>
@@ -1304,34 +1331,34 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C13" s="14" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D13" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E13" s="14" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="F13" s="14" t="s">
+      <x:c r="G13" s="14" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="G13" s="14" t="s">
+      <x:c r="H13" s="16">
+        <x:v>46112.0874409838</x:v>
+      </x:c>
+      <x:c r="I13" s="16">
+        <x:v>46134</x:v>
+      </x:c>
+      <x:c r="J13" s="15" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="H13" s="16">
-        <x:v>46126.3116678125</x:v>
-      </x:c>
-      <x:c r="I13" s="16">
-        <x:v>46196</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="s">
-        <x:v>46</x:v>
-      </x:c>
       <x:c r="K13" s="17" t="n">
-        <x:v>1950</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L13" s="18">
-        <x:v>46128.191368669</x:v>
+        <x:v>46125.1598529398</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
         <x:v>21</x:v>
@@ -1339,37 +1366,37 @@
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="14" t="s">
-        <x:v>47</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C14" s="14" t="s">
-        <x:v>32</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D14" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E14" s="14" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="F14" s="14" t="s">
+      <x:c r="G14" s="14" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="G14" s="14" t="s">
+      <x:c r="H14" s="16">
+        <x:v>46126.3116678125</x:v>
+      </x:c>
+      <x:c r="I14" s="16">
+        <x:v>46196</x:v>
+      </x:c>
+      <x:c r="J14" s="15" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="H14" s="16">
-        <x:v>46126.2721295949</x:v>
-      </x:c>
-      <x:c r="I14" s="16">
-        <x:v>46224</x:v>
-      </x:c>
-      <x:c r="J14" s="15" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="K14" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L14" s="18">
-        <x:v>46128.1955625</x:v>
+        <x:v>46128.191368669</x:v>
       </x:c>
       <x:c r="M14" s="14" t="s">
         <x:v>21</x:v>
@@ -1377,37 +1404,37 @@
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="14" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C15" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D15" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E15" s="14" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="F15" s="14" t="s">
+      <x:c r="G15" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="G15" s="14" t="s">
+      <x:c r="H15" s="16">
+        <x:v>46126.2721295949</x:v>
+      </x:c>
+      <x:c r="I15" s="16">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="J15" s="15" t="s">
         <x:v>55</x:v>
-      </x:c>
-      <x:c r="H15" s="16">
-        <x:v>46126.2873086111</x:v>
-      </x:c>
-      <x:c r="I15" s="16">
-        <x:v>46130</x:v>
-      </x:c>
-      <x:c r="J15" s="15" t="s">
-        <x:v>56</x:v>
       </x:c>
       <x:c r="K15" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L15" s="18">
-        <x:v>46127.0949605556</x:v>
+        <x:v>46128.1955625</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
         <x:v>21</x:v>
@@ -1415,10 +1442,10 @@
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="14" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C16" s="14" t="s">
-        <x:v>42</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D16" s="15" t="s">
         <x:v>16</x:v>
@@ -1433,10 +1460,10 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="H16" s="16">
-        <x:v>46126.3215783912</x:v>
+        <x:v>46125.335903912</x:v>
       </x:c>
       <x:c r="I16" s="16">
-        <x:v>46198</x:v>
+        <x:v>46203</x:v>
       </x:c>
       <x:c r="J16" s="15" t="s">
         <x:v>60</x:v>
@@ -1445,7 +1472,7 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L16" s="18">
-        <x:v>46128.1824279398</x:v>
+        <x:v>46134.2685065741</x:v>
       </x:c>
       <x:c r="M16" s="14" t="s">
         <x:v>21</x:v>
@@ -1453,99 +1480,173 @@
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="14" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C17" s="14" t="s">
-        <x:v>42</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D17" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E17" s="14" t="s">
-        <x:v>43</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F17" s="14" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G17" s="14" t="s">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H17" s="16">
-        <x:v>46126.3072273495</x:v>
+        <x:v>46126.2873086111</x:v>
       </x:c>
       <x:c r="I17" s="16">
-        <x:v>46189</x:v>
+        <x:v>46130</x:v>
       </x:c>
       <x:c r="J17" s="15" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="K17" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L17" s="18">
-        <x:v>46128.1930397685</x:v>
+        <x:v>46127.0949605556</x:v>
       </x:c>
       <x:c r="M17" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="20" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B20" s="19" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="C20" s="20" t="s"/>
-      <x:c r="D20" s="20" t="s"/>
-      <x:c r="E20" s="21" t="s"/>
-      <x:c r="F20" s="21" t="s"/>
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B18" s="14" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C18" s="14" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E18" s="14" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="G18" s="14" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="H18" s="16">
+        <x:v>46126.3215783912</x:v>
+      </x:c>
+      <x:c r="I18" s="16">
+        <x:v>46198</x:v>
+      </x:c>
+      <x:c r="J18" s="15" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="K18" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L18" s="18">
+        <x:v>46128.1824279398</x:v>
+      </x:c>
+      <x:c r="M18" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
     </x:row>
-    <x:row r="21" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B21" s="22" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C21" s="23" t="s"/>
-      <x:c r="D21" s="23" t="s"/>
-      <x:c r="E21" s="23" t="s"/>
-      <x:c r="F21" s="24" t="s">
-        <x:v>66</x:v>
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B19" s="14" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C19" s="14" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D19" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E19" s="14" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="G19" s="14" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="H19" s="16">
+        <x:v>46126.3072273495</x:v>
+      </x:c>
+      <x:c r="I19" s="16">
+        <x:v>46189</x:v>
+      </x:c>
+      <x:c r="J19" s="15" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="K19" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L19" s="18">
+        <x:v>46128.1930397685</x:v>
+      </x:c>
+      <x:c r="M19" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="25" t="s">
+    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="22" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B22" s="19" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C22" s="20" t="s"/>
+      <x:c r="D22" s="20" t="s"/>
+      <x:c r="E22" s="21" t="s"/>
+      <x:c r="F22" s="21" t="s"/>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B23" s="22" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C23" s="23" t="s"/>
+      <x:c r="D23" s="23" t="s"/>
+      <x:c r="E23" s="23" t="s"/>
+      <x:c r="F23" s="24" t="s">
+        <x:v>75</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B24" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C22" s="26" t="s"/>
-      <x:c r="D22" s="26" t="s"/>
-      <x:c r="E22" s="26" t="s"/>
-      <x:c r="F22" s="27" t="n">
-        <x:v>6</x:v>
+      <x:c r="C24" s="26" t="s"/>
+      <x:c r="D24" s="26" t="s"/>
+      <x:c r="E24" s="26" t="s"/>
+      <x:c r="F24" s="27" t="n">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="25" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C23" s="26" t="s"/>
-      <x:c r="D23" s="26" t="s"/>
-      <x:c r="E23" s="26" t="s"/>
-      <x:c r="F23" s="27" t="n">
-        <x:v>4</x:v>
+    <x:row r="25" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B25" s="25" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C25" s="26" t="s"/>
+      <x:c r="D25" s="26" t="s"/>
+      <x:c r="E25" s="26" t="s"/>
+      <x:c r="F25" s="27" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B24" s="28" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="C24" s="29" t="s"/>
-      <x:c r="D24" s="29" t="s"/>
-      <x:c r="E24" s="29" t="s"/>
-      <x:c r="F24" s="30" t="n">
-        <x:v>10</x:v>
+    <x:row r="26" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B26" s="28" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="C26" s="29" t="s"/>
+      <x:c r="D26" s="29" t="s"/>
+      <x:c r="E26" s="29" t="s"/>
+      <x:c r="F26" s="30" t="n">
+        <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2519,11 +2620,11 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B20:F20"/>
-    <x:mergeCell ref="B21:E21"/>
-    <x:mergeCell ref="B22:E22"/>
+    <x:mergeCell ref="B22:F22"/>
     <x:mergeCell ref="B23:E23"/>
     <x:mergeCell ref="B24:E24"/>
+    <x:mergeCell ref="B25:E25"/>
+    <x:mergeCell ref="B26:E26"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-JUNETTE-PONTILAR-evaluator-cache-serviceTracking-JUNETTE-PONTILAR-X-202501-202612.xlsx
+++ b/reports/service-tracking-report-JUNETTE-PONTILAR-evaluator-cache-serviceTracking-JUNETTE-PONTILAR-X-202501-202612.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="82">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -145,6 +145,21 @@
   </x:si>
   <x:si>
     <x:t>1518191</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORO GADGETS INC. (GRAPHIC GADGET STORES)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3E-1 THIRD LEVEL GAISANO PUERTO, PUERTO, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROX-MP-17-04-174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1446-993</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518243 A</x:t>
   </x:si>
   <x:si>
     <x:t>SOLIDMARK WEST, INC.</x:t>
@@ -1346,10 +1361,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="H13" s="16">
-        <x:v>46112.0874409838</x:v>
+        <x:v>46132.3880687384</x:v>
       </x:c>
       <x:c r="I13" s="16">
-        <x:v>46134</x:v>
+        <x:v>46138</x:v>
       </x:c>
       <x:c r="J13" s="15" t="s">
         <x:v>45</x:v>
@@ -1358,7 +1373,7 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L13" s="18">
-        <x:v>46125.1598529398</x:v>
+        <x:v>46135.1691307292</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
         <x:v>21</x:v>
@@ -1384,19 +1399,19 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="H14" s="16">
-        <x:v>46126.3116678125</x:v>
+        <x:v>46112.0874409838</x:v>
       </x:c>
       <x:c r="I14" s="16">
-        <x:v>46196</x:v>
+        <x:v>46134</x:v>
       </x:c>
       <x:c r="J14" s="15" t="s">
         <x:v>50</x:v>
       </x:c>
       <x:c r="K14" s="17" t="n">
-        <x:v>1950</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L14" s="18">
-        <x:v>46128.191368669</x:v>
+        <x:v>46125.1598529398</x:v>
       </x:c>
       <x:c r="M14" s="14" t="s">
         <x:v>21</x:v>
@@ -1404,10 +1419,10 @@
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="14" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="C15" s="14" t="s">
-        <x:v>36</x:v>
       </x:c>
       <x:c r="D15" s="15" t="s">
         <x:v>16</x:v>
@@ -1422,19 +1437,19 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="H15" s="16">
-        <x:v>46126.2721295949</x:v>
+        <x:v>46126.3116678125</x:v>
       </x:c>
       <x:c r="I15" s="16">
-        <x:v>46224</x:v>
+        <x:v>46196</x:v>
       </x:c>
       <x:c r="J15" s="15" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="K15" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L15" s="18">
-        <x:v>46128.1955625</x:v>
+        <x:v>46128.191368669</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
         <x:v>21</x:v>
@@ -1442,10 +1457,10 @@
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="14" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C16" s="14" t="s">
-        <x:v>56</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D16" s="15" t="s">
         <x:v>16</x:v>
@@ -1460,10 +1475,10 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="H16" s="16">
-        <x:v>46125.335903912</x:v>
+        <x:v>46126.2721295949</x:v>
       </x:c>
       <x:c r="I16" s="16">
-        <x:v>46203</x:v>
+        <x:v>46224</x:v>
       </x:c>
       <x:c r="J16" s="15" t="s">
         <x:v>60</x:v>
@@ -1472,7 +1487,7 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L16" s="18">
-        <x:v>46134.2685065741</x:v>
+        <x:v>46128.1955625</x:v>
       </x:c>
       <x:c r="M16" s="14" t="s">
         <x:v>21</x:v>
@@ -1480,7 +1495,7 @@
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="14" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C17" s="14" t="s">
         <x:v>61</x:v>
@@ -1498,10 +1513,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="H17" s="16">
-        <x:v>46126.2873086111</x:v>
+        <x:v>46125.335903912</x:v>
       </x:c>
       <x:c r="I17" s="16">
-        <x:v>46130</x:v>
+        <x:v>46203</x:v>
       </x:c>
       <x:c r="J17" s="15" t="s">
         <x:v>65</x:v>
@@ -1510,7 +1525,7 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L17" s="18">
-        <x:v>46127.0949605556</x:v>
+        <x:v>46134.2685065741</x:v>
       </x:c>
       <x:c r="M17" s="14" t="s">
         <x:v>21</x:v>
@@ -1518,37 +1533,37 @@
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="14" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C18" s="14" t="s">
-        <x:v>46</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D18" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E18" s="14" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F18" s="14" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G18" s="14" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="H18" s="16">
-        <x:v>46126.3215783912</x:v>
+        <x:v>46126.2873086111</x:v>
       </x:c>
       <x:c r="I18" s="16">
-        <x:v>46198</x:v>
+        <x:v>46130</x:v>
       </x:c>
       <x:c r="J18" s="15" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="K18" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L18" s="18">
-        <x:v>46128.1824279398</x:v>
+        <x:v>46127.0949605556</x:v>
       </x:c>
       <x:c r="M18" s="14" t="s">
         <x:v>21</x:v>
@@ -1556,98 +1571,135 @@
     </x:row>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
       <x:c r="B19" s="14" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C19" s="14" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="C19" s="14" t="s">
-        <x:v>46</x:v>
       </x:c>
       <x:c r="D19" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E19" s="14" t="s">
-        <x:v>47</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F19" s="14" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="G19" s="14" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="H19" s="16">
-        <x:v>46126.3072273495</x:v>
+        <x:v>46126.3215783912</x:v>
       </x:c>
       <x:c r="I19" s="16">
-        <x:v>46189</x:v>
+        <x:v>46198</x:v>
       </x:c>
       <x:c r="J19" s="15" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="K19" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L19" s="18">
-        <x:v>46128.1930397685</x:v>
+        <x:v>46128.1824279398</x:v>
       </x:c>
       <x:c r="M19" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B20" s="14" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C20" s="14" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D20" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E20" s="14" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="G20" s="14" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="H20" s="16">
+        <x:v>46126.3072273495</x:v>
+      </x:c>
+      <x:c r="I20" s="16">
+        <x:v>46189</x:v>
+      </x:c>
+      <x:c r="J20" s="15" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="K20" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L20" s="18">
+        <x:v>46128.1930397685</x:v>
+      </x:c>
+      <x:c r="M20" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="22" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B22" s="19" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C22" s="20" t="s"/>
-      <x:c r="D22" s="20" t="s"/>
-      <x:c r="E22" s="21" t="s"/>
-      <x:c r="F22" s="21" t="s"/>
+    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="23" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B23" s="19" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C23" s="20" t="s"/>
+      <x:c r="D23" s="20" t="s"/>
+      <x:c r="E23" s="21" t="s"/>
+      <x:c r="F23" s="21" t="s"/>
     </x:row>
-    <x:row r="23" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B23" s="22" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="C23" s="23" t="s"/>
-      <x:c r="D23" s="23" t="s"/>
-      <x:c r="E23" s="23" t="s"/>
-      <x:c r="F23" s="24" t="s">
-        <x:v>75</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="25" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C24" s="26" t="s"/>
-      <x:c r="D24" s="26" t="s"/>
-      <x:c r="E24" s="26" t="s"/>
-      <x:c r="F24" s="27" t="n">
-        <x:v>7</x:v>
+    <x:row r="24" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B24" s="22" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C24" s="23" t="s"/>
+      <x:c r="D24" s="23" t="s"/>
+      <x:c r="E24" s="23" t="s"/>
+      <x:c r="F24" s="24" t="s">
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="18" customHeight="1">
       <x:c r="B25" s="25" t="s">
-        <x:v>51</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C25" s="26" t="s"/>
       <x:c r="D25" s="26" t="s"/>
       <x:c r="E25" s="26" t="s"/>
       <x:c r="F25" s="27" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B26" s="25" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C26" s="26" t="s"/>
+      <x:c r="D26" s="26" t="s"/>
+      <x:c r="E26" s="26" t="s"/>
+      <x:c r="F26" s="27" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B26" s="28" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="C26" s="29" t="s"/>
-      <x:c r="D26" s="29" t="s"/>
-      <x:c r="E26" s="29" t="s"/>
-      <x:c r="F26" s="30" t="n">
-        <x:v>12</x:v>
+    <x:row r="27" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B27" s="28" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="C27" s="29" t="s"/>
+      <x:c r="D27" s="29" t="s"/>
+      <x:c r="E27" s="29" t="s"/>
+      <x:c r="F27" s="30" t="n">
+        <x:v>13</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2620,11 +2672,11 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B22:F22"/>
-    <x:mergeCell ref="B23:E23"/>
+    <x:mergeCell ref="B23:F23"/>
     <x:mergeCell ref="B24:E24"/>
     <x:mergeCell ref="B25:E25"/>
     <x:mergeCell ref="B26:E26"/>
+    <x:mergeCell ref="B27:E27"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-JUNETTE-PONTILAR-evaluator-cache-serviceTracking-JUNETTE-PONTILAR-X-202501-202612.xlsx
+++ b/reports/service-tracking-report-JUNETTE-PONTILAR-evaluator-cache-serviceTracking-JUNETTE-PONTILAR-X-202501-202612.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="82">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="99">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -66,6 +66,45 @@
     <x:t>BY</x:t>
   </x:si>
   <x:si>
+    <x:t>Dealer Permit (NEW)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELLTY MOBILE INC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NEW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GAISANO TUBOD,PABLACION,TUBOD LANAO DEL NORTE, POBLACION, Tubod (Capital), Lanao Del Norte</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROX-08615-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1445-013</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518266 A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CHERYL MAY DELOSO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LAPTAP ENTERPRISES, INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2F, Lifestyle District Corrales Ext, Brgy. 23, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MP-ROX-08533-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1439-984</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518270 A</x:t>
+  </x:si>
+  <x:si>
     <x:t>Dealer Permit (RENEWAL)</x:t>
   </x:si>
   <x:si>
@@ -87,9 +126,6 @@
     <x:t>1518210 A</x:t>
   </x:si>
   <x:si>
-    <x:t>CHERYL MAY DELOSO</x:t>
-  </x:si>
-  <x:si>
     <x:t>NADAL BDLG NATIONAL HIGHWAY, BARANGAY 3, Gingoog City, Misamis Oriental</x:t>
   </x:si>
   <x:si>
@@ -193,6 +229,21 @@
   </x:si>
   <x:si>
     <x:t>Retailer/Reseller Permit (RENEWAL)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HO TSAYKI INC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T-29 &amp; T-30 citymall bulua, Bulua, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROX-MRR-19-05-425</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1449-395</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518265 A</x:t>
   </x:si>
   <x:si>
     <x:t>WEST WING LKKS CENTER, Barangay 31, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
@@ -1171,19 +1222,19 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="H8" s="16">
-        <x:v>46132.2785644329</x:v>
+        <x:v>46132.313701713</x:v>
       </x:c>
       <x:c r="I8" s="16">
-        <x:v>46135</x:v>
+        <x:v>46132.3137205208</x:v>
       </x:c>
       <x:c r="J8" s="15" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="K8" s="17" t="n">
-        <x:v>1950</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L8" s="18">
-        <x:v>46133.1152077083</x:v>
+        <x:v>46139.230364294</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
@@ -1194,34 +1245,34 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>15</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D9" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H9" s="16">
-        <x:v>46128.2089466088</x:v>
+        <x:v>46129.4086055787</x:v>
       </x:c>
       <x:c r="I9" s="16">
-        <x:v>46135</x:v>
+        <x:v>46129.4086256481</x:v>
       </x:c>
       <x:c r="J9" s="15" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K9" s="17" t="n">
-        <x:v>1950</x:v>
+        <x:v>2130</x:v>
       </x:c>
       <x:c r="L9" s="18">
-        <x:v>46134.3002672917</x:v>
+        <x:v>46139.3272522222</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
@@ -1229,37 +1280,37 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C10" s="14" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D10" s="15" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E10" s="14" t="s">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F10" s="14" t="s">
-        <x:v>28</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G10" s="14" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H10" s="16">
-        <x:v>46128.1699027199</x:v>
+        <x:v>46132.2785644329</x:v>
       </x:c>
       <x:c r="I10" s="16">
-        <x:v>46136</x:v>
+        <x:v>46135</x:v>
       </x:c>
       <x:c r="J10" s="15" t="s">
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="K10" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L10" s="18">
-        <x:v>46128.349008206</x:v>
+        <x:v>46133.1152077083</x:v>
       </x:c>
       <x:c r="M10" s="14" t="s">
         <x:v>21</x:v>
@@ -1267,37 +1318,37 @@
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C11" s="14" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D11" s="15" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E11" s="14" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F11" s="14" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G11" s="14" t="s">
-        <x:v>34</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H11" s="16">
-        <x:v>46133.2374101505</x:v>
+        <x:v>46128.2089466088</x:v>
       </x:c>
       <x:c r="I11" s="16">
         <x:v>46135</x:v>
       </x:c>
       <x:c r="J11" s="15" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="K11" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L11" s="18">
-        <x:v>46134.0815209838</x:v>
+        <x:v>46134.3002672917</x:v>
       </x:c>
       <x:c r="M11" s="14" t="s">
         <x:v>21</x:v>
@@ -1305,37 +1356,37 @@
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="14" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C12" s="14" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D12" s="15" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E12" s="14" t="s">
-        <x:v>37</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F12" s="14" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G12" s="14" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H12" s="16">
-        <x:v>46126.2900560185</x:v>
+        <x:v>46128.1699027199</x:v>
       </x:c>
       <x:c r="I12" s="16">
-        <x:v>46162</x:v>
+        <x:v>46136</x:v>
       </x:c>
       <x:c r="J12" s="15" t="s">
-        <x:v>40</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="K12" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L12" s="18">
-        <x:v>46128.194732662</x:v>
+        <x:v>46128.349008206</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
         <x:v>21</x:v>
@@ -1343,37 +1394,37 @@
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="14" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C13" s="14" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D13" s="15" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E13" s="14" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F13" s="14" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G13" s="14" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H13" s="16">
-        <x:v>46132.3880687384</x:v>
+        <x:v>46133.2374101505</x:v>
       </x:c>
       <x:c r="I13" s="16">
-        <x:v>46138</x:v>
+        <x:v>46135</x:v>
       </x:c>
       <x:c r="J13" s="15" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K13" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L13" s="18">
-        <x:v>46135.1691307292</x:v>
+        <x:v>46134.0815209838</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
         <x:v>21</x:v>
@@ -1381,37 +1432,37 @@
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="14" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C14" s="14" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D14" s="15" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E14" s="14" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F14" s="14" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G14" s="14" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H14" s="16">
-        <x:v>46112.0874409838</x:v>
+        <x:v>46126.2900560185</x:v>
       </x:c>
       <x:c r="I14" s="16">
-        <x:v>46134</x:v>
+        <x:v>46162</x:v>
       </x:c>
       <x:c r="J14" s="15" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K14" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L14" s="18">
-        <x:v>46125.1598529398</x:v>
+        <x:v>46128.194732662</x:v>
       </x:c>
       <x:c r="M14" s="14" t="s">
         <x:v>21</x:v>
@@ -1419,37 +1470,37 @@
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="14" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C15" s="14" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D15" s="15" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E15" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F15" s="14" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G15" s="14" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H15" s="16">
-        <x:v>46126.3116678125</x:v>
+        <x:v>46132.3880687384</x:v>
       </x:c>
       <x:c r="I15" s="16">
-        <x:v>46196</x:v>
+        <x:v>46138</x:v>
       </x:c>
       <x:c r="J15" s="15" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="K15" s="17" t="n">
-        <x:v>1950</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L15" s="18">
-        <x:v>46128.191368669</x:v>
+        <x:v>46135.1691307292</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
         <x:v>21</x:v>
@@ -1457,37 +1508,37 @@
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="14" t="s">
-        <x:v>56</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C16" s="14" t="s">
-        <x:v>36</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D16" s="15" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E16" s="14" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F16" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G16" s="14" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H16" s="16">
-        <x:v>46126.2721295949</x:v>
+        <x:v>46112.0874409838</x:v>
       </x:c>
       <x:c r="I16" s="16">
-        <x:v>46224</x:v>
+        <x:v>46134</x:v>
       </x:c>
       <x:c r="J16" s="15" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="K16" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L16" s="18">
-        <x:v>46128.1955625</x:v>
+        <x:v>46125.1598529398</x:v>
       </x:c>
       <x:c r="M16" s="14" t="s">
         <x:v>21</x:v>
@@ -1495,37 +1546,37 @@
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="14" t="s">
-        <x:v>56</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C17" s="14" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D17" s="15" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E17" s="14" t="s">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F17" s="14" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="G17" s="14" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="H17" s="16">
-        <x:v>46125.335903912</x:v>
+        <x:v>46126.3116678125</x:v>
       </x:c>
       <x:c r="I17" s="16">
-        <x:v>46203</x:v>
+        <x:v>46196</x:v>
       </x:c>
       <x:c r="J17" s="15" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="K17" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L17" s="18">
-        <x:v>46134.2685065741</x:v>
+        <x:v>46128.191368669</x:v>
       </x:c>
       <x:c r="M17" s="14" t="s">
         <x:v>21</x:v>
@@ -1533,37 +1584,37 @@
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="14" t="s">
-        <x:v>56</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C18" s="14" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D18" s="15" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E18" s="14" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F18" s="14" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="G18" s="14" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="H18" s="16">
-        <x:v>46126.2873086111</x:v>
+        <x:v>46134.0293580208</x:v>
       </x:c>
       <x:c r="I18" s="16">
-        <x:v>46130</x:v>
+        <x:v>46144</x:v>
       </x:c>
       <x:c r="J18" s="15" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K18" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L18" s="18">
-        <x:v>46127.0949605556</x:v>
+        <x:v>46139.2265670718</x:v>
       </x:c>
       <x:c r="M18" s="14" t="s">
         <x:v>21</x:v>
@@ -1571,37 +1622,37 @@
     </x:row>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
       <x:c r="B19" s="14" t="s">
-        <x:v>56</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C19" s="14" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D19" s="15" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E19" s="14" t="s">
-        <x:v>71</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F19" s="14" t="s">
-        <x:v>72</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="G19" s="14" t="s">
-        <x:v>73</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="H19" s="16">
-        <x:v>46126.3215783912</x:v>
+        <x:v>46126.2721295949</x:v>
       </x:c>
       <x:c r="I19" s="16">
-        <x:v>46198</x:v>
+        <x:v>46224</x:v>
       </x:c>
       <x:c r="J19" s="15" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="K19" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L19" s="18">
-        <x:v>46128.1824279398</x:v>
+        <x:v>46128.1955625</x:v>
       </x:c>
       <x:c r="M19" s="14" t="s">
         <x:v>21</x:v>
@@ -1609,101 +1660,222 @@
     </x:row>
     <x:row r="20" spans="1:28" ht="30" customHeight="1">
       <x:c r="B20" s="14" t="s">
-        <x:v>56</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C20" s="14" t="s">
-        <x:v>51</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D20" s="15" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E20" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F20" s="14" t="s">
-        <x:v>75</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="G20" s="14" t="s">
-        <x:v>76</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H20" s="16">
-        <x:v>46126.3072273495</x:v>
+        <x:v>46125.335903912</x:v>
       </x:c>
       <x:c r="I20" s="16">
-        <x:v>46189</x:v>
+        <x:v>46203</x:v>
       </x:c>
       <x:c r="J20" s="15" t="s">
-        <x:v>77</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="K20" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L20" s="18">
-        <x:v>46128.1930397685</x:v>
+        <x:v>46134.2685065741</x:v>
       </x:c>
       <x:c r="M20" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="21" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B21" s="14" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C21" s="14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D21" s="15" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E21" s="14" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="G21" s="14" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="H21" s="16">
+        <x:v>46126.2873086111</x:v>
+      </x:c>
+      <x:c r="I21" s="16">
+        <x:v>46130</x:v>
+      </x:c>
+      <x:c r="J21" s="15" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="K21" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L21" s="18">
+        <x:v>46127.0949605556</x:v>
+      </x:c>
+      <x:c r="M21" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B22" s="14" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C22" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="D22" s="15" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E22" s="14" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="G22" s="14" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="H22" s="16">
+        <x:v>46126.3215783912</x:v>
+      </x:c>
+      <x:c r="I22" s="16">
+        <x:v>46198</x:v>
+      </x:c>
+      <x:c r="J22" s="15" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="K22" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L22" s="18">
+        <x:v>46128.1824279398</x:v>
+      </x:c>
+      <x:c r="M22" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="23" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B23" s="19" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C23" s="20" t="s"/>
-      <x:c r="D23" s="20" t="s"/>
-      <x:c r="E23" s="21" t="s"/>
-      <x:c r="F23" s="21" t="s"/>
+      <x:c r="B23" s="14" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C23" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="D23" s="15" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E23" s="14" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="G23" s="14" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="H23" s="16">
+        <x:v>46126.3072273495</x:v>
+      </x:c>
+      <x:c r="I23" s="16">
+        <x:v>46189</x:v>
+      </x:c>
+      <x:c r="J23" s="15" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="K23" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L23" s="18">
+        <x:v>46128.1930397685</x:v>
+      </x:c>
+      <x:c r="M23" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
     </x:row>
-    <x:row r="24" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B24" s="22" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C24" s="23" t="s"/>
-      <x:c r="D24" s="23" t="s"/>
-      <x:c r="E24" s="23" t="s"/>
-      <x:c r="F24" s="24" t="s">
-        <x:v>80</x:v>
-      </x:c>
+    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="26" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B26" s="19" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C26" s="20" t="s"/>
+      <x:c r="D26" s="20" t="s"/>
+      <x:c r="E26" s="21" t="s"/>
+      <x:c r="F26" s="21" t="s"/>
     </x:row>
-    <x:row r="25" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B25" s="25" t="s">
+    <x:row r="27" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B27" s="22" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C27" s="23" t="s"/>
+      <x:c r="D27" s="23" t="s"/>
+      <x:c r="E27" s="23" t="s"/>
+      <x:c r="F27" s="24" t="s">
+        <x:v>97</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B28" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C25" s="26" t="s"/>
-      <x:c r="D25" s="26" t="s"/>
-      <x:c r="E25" s="26" t="s"/>
-      <x:c r="F25" s="27" t="n">
+      <x:c r="C28" s="26" t="s"/>
+      <x:c r="D28" s="26" t="s"/>
+      <x:c r="E28" s="26" t="s"/>
+      <x:c r="F28" s="27" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B29" s="25" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C29" s="26" t="s"/>
+      <x:c r="D29" s="26" t="s"/>
+      <x:c r="E29" s="26" t="s"/>
+      <x:c r="F29" s="27" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="25" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C26" s="26" t="s"/>
-      <x:c r="D26" s="26" t="s"/>
-      <x:c r="E26" s="26" t="s"/>
-      <x:c r="F26" s="27" t="n">
-        <x:v>5</x:v>
+    <x:row r="30" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B30" s="25" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C30" s="26" t="s"/>
+      <x:c r="D30" s="26" t="s"/>
+      <x:c r="E30" s="26" t="s"/>
+      <x:c r="F30" s="27" t="n">
+        <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B27" s="28" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="C27" s="29" t="s"/>
-      <x:c r="D27" s="29" t="s"/>
-      <x:c r="E27" s="29" t="s"/>
-      <x:c r="F27" s="30" t="n">
-        <x:v>13</x:v>
+    <x:row r="31" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B31" s="28" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C31" s="29" t="s"/>
+      <x:c r="D31" s="29" t="s"/>
+      <x:c r="E31" s="29" t="s"/>
+      <x:c r="F31" s="30" t="n">
+        <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2667,16 +2839,17 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="9">
+  <x:mergeCells count="10">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B23:F23"/>
-    <x:mergeCell ref="B24:E24"/>
-    <x:mergeCell ref="B25:E25"/>
-    <x:mergeCell ref="B26:E26"/>
+    <x:mergeCell ref="B26:F26"/>
     <x:mergeCell ref="B27:E27"/>
+    <x:mergeCell ref="B28:E28"/>
+    <x:mergeCell ref="B29:E29"/>
+    <x:mergeCell ref="B30:E30"/>
+    <x:mergeCell ref="B31:E31"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-JUNETTE-PONTILAR-evaluator-cache-serviceTracking-JUNETTE-PONTILAR-X-202501-202612.xlsx
+++ b/reports/service-tracking-report-JUNETTE-PONTILAR-evaluator-cache-serviceTracking-JUNETTE-PONTILAR-X-202501-202612.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="99">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="103">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -114,6 +114,30 @@
     <x:t>REN</x:t>
   </x:si>
   <x:si>
+    <x:t>RIZAL AVENUE, 50TH DISTRICT, Ozamis City, Misamis Occidental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18-REDP-CAG-01370</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1452-386</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518271 A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NADAL BDLG NATIONAL HIGHWAY, BARANGAY 3, Gingoog City, Misamis Oriental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18-REDP-CAG-01361</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1436-764</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518230 A</x:t>
+  </x:si>
+  <x:si>
     <x:t>P-3 NATIONAL HIGHWAY, POBLACION, Alubijid, Misamis Oriental</x:t>
   </x:si>
   <x:si>
@@ -124,18 +148,6 @@
   </x:si>
   <x:si>
     <x:t>1518210 A</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NADAL BDLG NATIONAL HIGHWAY, BARANGAY 3, Gingoog City, Misamis Oriental</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18-REDP-CAG-01361</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1436-764</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1518230 A</x:t>
   </x:si>
   <x:si>
     <x:t>EMCOR INCORPORATED</x:t>
@@ -1298,10 +1310,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="H10" s="16">
-        <x:v>46132.2785644329</x:v>
+        <x:v>46137.0314533796</x:v>
       </x:c>
       <x:c r="I10" s="16">
-        <x:v>46135</x:v>
+        <x:v>46149</x:v>
       </x:c>
       <x:c r="J10" s="15" t="s">
         <x:v>33</x:v>
@@ -1310,7 +1322,7 @@
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L10" s="18">
-        <x:v>46133.1152077083</x:v>
+        <x:v>46139.3366940046</x:v>
       </x:c>
       <x:c r="M10" s="14" t="s">
         <x:v>21</x:v>
@@ -1359,34 +1371,34 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C12" s="14" t="s">
-        <x:v>38</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D12" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="E12" s="14" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="F12" s="14" t="s">
+      <x:c r="G12" s="14" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G12" s="14" t="s">
+      <x:c r="H12" s="16">
+        <x:v>46132.2785644329</x:v>
+      </x:c>
+      <x:c r="I12" s="16">
+        <x:v>46135</x:v>
+      </x:c>
+      <x:c r="J12" s="15" t="s">
         <x:v>41</x:v>
-      </x:c>
-      <x:c r="H12" s="16">
-        <x:v>46128.1699027199</x:v>
-      </x:c>
-      <x:c r="I12" s="16">
-        <x:v>46136</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="s">
-        <x:v>42</x:v>
       </x:c>
       <x:c r="K12" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L12" s="18">
-        <x:v>46128.349008206</x:v>
+        <x:v>46133.1152077083</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
         <x:v>21</x:v>
@@ -1397,34 +1409,34 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C13" s="14" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D13" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="E13" s="14" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="F13" s="14" t="s">
+      <x:c r="G13" s="14" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="G13" s="14" t="s">
+      <x:c r="H13" s="16">
+        <x:v>46128.1699027199</x:v>
+      </x:c>
+      <x:c r="I13" s="16">
+        <x:v>46136</x:v>
+      </x:c>
+      <x:c r="J13" s="15" t="s">
         <x:v>46</x:v>
-      </x:c>
-      <x:c r="H13" s="16">
-        <x:v>46133.2374101505</x:v>
-      </x:c>
-      <x:c r="I13" s="16">
-        <x:v>46135</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="s">
-        <x:v>47</x:v>
       </x:c>
       <x:c r="K13" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L13" s="18">
-        <x:v>46134.0815209838</x:v>
+        <x:v>46128.349008206</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
         <x:v>21</x:v>
@@ -1435,34 +1447,34 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C14" s="14" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D14" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="E14" s="14" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="F14" s="14" t="s">
+      <x:c r="G14" s="14" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="G14" s="14" t="s">
+      <x:c r="H14" s="16">
+        <x:v>46133.2374101505</x:v>
+      </x:c>
+      <x:c r="I14" s="16">
+        <x:v>46135</x:v>
+      </x:c>
+      <x:c r="J14" s="15" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="H14" s="16">
-        <x:v>46126.2900560185</x:v>
-      </x:c>
-      <x:c r="I14" s="16">
-        <x:v>46162</x:v>
-      </x:c>
-      <x:c r="J14" s="15" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="K14" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L14" s="18">
-        <x:v>46128.194732662</x:v>
+        <x:v>46134.0815209838</x:v>
       </x:c>
       <x:c r="M14" s="14" t="s">
         <x:v>21</x:v>
@@ -1473,34 +1485,34 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C15" s="14" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D15" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="E15" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="F15" s="14" t="s">
+      <x:c r="G15" s="14" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="G15" s="14" t="s">
+      <x:c r="H15" s="16">
+        <x:v>46126.2900560185</x:v>
+      </x:c>
+      <x:c r="I15" s="16">
+        <x:v>46162</x:v>
+      </x:c>
+      <x:c r="J15" s="15" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="H15" s="16">
-        <x:v>46132.3880687384</x:v>
-      </x:c>
-      <x:c r="I15" s="16">
-        <x:v>46138</x:v>
-      </x:c>
-      <x:c r="J15" s="15" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="K15" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L15" s="18">
-        <x:v>46135.1691307292</x:v>
+        <x:v>46128.194732662</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
         <x:v>21</x:v>
@@ -1511,34 +1523,34 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C16" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D16" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="E16" s="14" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="F16" s="14" t="s">
+      <x:c r="G16" s="14" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="G16" s="14" t="s">
+      <x:c r="H16" s="16">
+        <x:v>46132.3880687384</x:v>
+      </x:c>
+      <x:c r="I16" s="16">
+        <x:v>46138</x:v>
+      </x:c>
+      <x:c r="J16" s="15" t="s">
         <x:v>61</x:v>
-      </x:c>
-      <x:c r="H16" s="16">
-        <x:v>46112.0874409838</x:v>
-      </x:c>
-      <x:c r="I16" s="16">
-        <x:v>46134</x:v>
-      </x:c>
-      <x:c r="J16" s="15" t="s">
-        <x:v>62</x:v>
       </x:c>
       <x:c r="K16" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L16" s="18">
-        <x:v>46125.1598529398</x:v>
+        <x:v>46135.1691307292</x:v>
       </x:c>
       <x:c r="M16" s="14" t="s">
         <x:v>21</x:v>
@@ -1549,34 +1561,34 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C17" s="14" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D17" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="E17" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="F17" s="14" t="s">
+      <x:c r="G17" s="14" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="G17" s="14" t="s">
+      <x:c r="H17" s="16">
+        <x:v>46112.0874409838</x:v>
+      </x:c>
+      <x:c r="I17" s="16">
+        <x:v>46134</x:v>
+      </x:c>
+      <x:c r="J17" s="15" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="H17" s="16">
-        <x:v>46126.3116678125</x:v>
-      </x:c>
-      <x:c r="I17" s="16">
-        <x:v>46196</x:v>
-      </x:c>
-      <x:c r="J17" s="15" t="s">
-        <x:v>67</x:v>
-      </x:c>
       <x:c r="K17" s="17" t="n">
-        <x:v>1950</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L17" s="18">
-        <x:v>46128.191368669</x:v>
+        <x:v>46125.1598529398</x:v>
       </x:c>
       <x:c r="M17" s="14" t="s">
         <x:v>21</x:v>
@@ -1584,37 +1596,37 @@
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="14" t="s">
-        <x:v>68</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C18" s="14" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D18" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="E18" s="14" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="G18" s="14" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="F18" s="14" t="s">
+      <x:c r="H18" s="16">
+        <x:v>46126.3116678125</x:v>
+      </x:c>
+      <x:c r="I18" s="16">
+        <x:v>46196</x:v>
+      </x:c>
+      <x:c r="J18" s="15" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="G18" s="14" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="H18" s="16">
-        <x:v>46134.0293580208</x:v>
-      </x:c>
-      <x:c r="I18" s="16">
-        <x:v>46144</x:v>
-      </x:c>
-      <x:c r="J18" s="15" t="s">
-        <x:v>73</x:v>
-      </x:c>
       <x:c r="K18" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L18" s="18">
-        <x:v>46139.2265670718</x:v>
+        <x:v>46128.191368669</x:v>
       </x:c>
       <x:c r="M18" s="14" t="s">
         <x:v>21</x:v>
@@ -1622,10 +1634,10 @@
     </x:row>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
       <x:c r="B19" s="14" t="s">
-        <x:v>68</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C19" s="14" t="s">
-        <x:v>48</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D19" s="15" t="s">
         <x:v>29</x:v>
@@ -1640,10 +1652,10 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="H19" s="16">
-        <x:v>46126.2721295949</x:v>
+        <x:v>46134.0293580208</x:v>
       </x:c>
       <x:c r="I19" s="16">
-        <x:v>46224</x:v>
+        <x:v>46144</x:v>
       </x:c>
       <x:c r="J19" s="15" t="s">
         <x:v>77</x:v>
@@ -1652,7 +1664,7 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L19" s="18">
-        <x:v>46128.1955625</x:v>
+        <x:v>46139.2265670718</x:v>
       </x:c>
       <x:c r="M19" s="14" t="s">
         <x:v>21</x:v>
@@ -1660,37 +1672,37 @@
     </x:row>
     <x:row r="20" spans="1:28" ht="30" customHeight="1">
       <x:c r="B20" s="14" t="s">
-        <x:v>68</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C20" s="14" t="s">
-        <x:v>78</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D20" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="E20" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="F20" s="14" t="s">
+      <x:c r="G20" s="14" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="G20" s="14" t="s">
+      <x:c r="H20" s="16">
+        <x:v>46126.2721295949</x:v>
+      </x:c>
+      <x:c r="I20" s="16">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="J20" s="15" t="s">
         <x:v>81</x:v>
-      </x:c>
-      <x:c r="H20" s="16">
-        <x:v>46125.335903912</x:v>
-      </x:c>
-      <x:c r="I20" s="16">
-        <x:v>46203</x:v>
-      </x:c>
-      <x:c r="J20" s="15" t="s">
-        <x:v>82</x:v>
       </x:c>
       <x:c r="K20" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L20" s="18">
-        <x:v>46134.2685065741</x:v>
+        <x:v>46128.1955625</x:v>
       </x:c>
       <x:c r="M20" s="14" t="s">
         <x:v>21</x:v>
@@ -1698,37 +1710,37 @@
     </x:row>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
       <x:c r="B21" s="14" t="s">
-        <x:v>68</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C21" s="14" t="s">
-        <x:v>83</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D21" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="E21" s="14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="F21" s="14" t="s">
+      <x:c r="G21" s="14" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="G21" s="14" t="s">
+      <x:c r="H21" s="16">
+        <x:v>46125.335903912</x:v>
+      </x:c>
+      <x:c r="I21" s="16">
+        <x:v>46203</x:v>
+      </x:c>
+      <x:c r="J21" s="15" t="s">
         <x:v>86</x:v>
-      </x:c>
-      <x:c r="H21" s="16">
-        <x:v>46126.2873086111</x:v>
-      </x:c>
-      <x:c r="I21" s="16">
-        <x:v>46130</x:v>
-      </x:c>
-      <x:c r="J21" s="15" t="s">
-        <x:v>87</x:v>
       </x:c>
       <x:c r="K21" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L21" s="18">
-        <x:v>46127.0949605556</x:v>
+        <x:v>46134.2685065741</x:v>
       </x:c>
       <x:c r="M21" s="14" t="s">
         <x:v>21</x:v>
@@ -1736,10 +1748,10 @@
     </x:row>
     <x:row r="22" spans="1:28" ht="30" customHeight="1">
       <x:c r="B22" s="14" t="s">
-        <x:v>68</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C22" s="14" t="s">
-        <x:v>63</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D22" s="15" t="s">
         <x:v>29</x:v>
@@ -1754,10 +1766,10 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="H22" s="16">
-        <x:v>46126.3215783912</x:v>
+        <x:v>46126.2873086111</x:v>
       </x:c>
       <x:c r="I22" s="16">
-        <x:v>46198</x:v>
+        <x:v>46130</x:v>
       </x:c>
       <x:c r="J22" s="15" t="s">
         <x:v>91</x:v>
@@ -1766,7 +1778,7 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L22" s="18">
-        <x:v>46128.1824279398</x:v>
+        <x:v>46127.0949605556</x:v>
       </x:c>
       <x:c r="M22" s="14" t="s">
         <x:v>21</x:v>
@@ -1774,109 +1786,146 @@
     </x:row>
     <x:row r="23" spans="1:28" ht="30" customHeight="1">
       <x:c r="B23" s="14" t="s">
-        <x:v>68</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C23" s="14" t="s">
-        <x:v>63</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D23" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="E23" s="14" t="s">
-        <x:v>64</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F23" s="14" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G23" s="14" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="H23" s="16">
-        <x:v>46126.3072273495</x:v>
+        <x:v>46126.3215783912</x:v>
       </x:c>
       <x:c r="I23" s="16">
-        <x:v>46189</x:v>
+        <x:v>46198</x:v>
       </x:c>
       <x:c r="J23" s="15" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="K23" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L23" s="18">
-        <x:v>46128.1930397685</x:v>
+        <x:v>46128.1824279398</x:v>
       </x:c>
       <x:c r="M23" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="24" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B24" s="14" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="C24" s="14" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D24" s="15" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E24" s="14" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="G24" s="14" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="H24" s="16">
+        <x:v>46126.3072273495</x:v>
+      </x:c>
+      <x:c r="I24" s="16">
+        <x:v>46189</x:v>
+      </x:c>
+      <x:c r="J24" s="15" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="K24" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L24" s="18">
+        <x:v>46128.1930397685</x:v>
+      </x:c>
+      <x:c r="M24" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="26" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B26" s="19" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="C26" s="20" t="s"/>
-      <x:c r="D26" s="20" t="s"/>
-      <x:c r="E26" s="21" t="s"/>
-      <x:c r="F26" s="21" t="s"/>
+    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="27" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B27" s="19" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C27" s="20" t="s"/>
+      <x:c r="D27" s="20" t="s"/>
+      <x:c r="E27" s="21" t="s"/>
+      <x:c r="F27" s="21" t="s"/>
     </x:row>
-    <x:row r="27" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B27" s="22" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="C27" s="23" t="s"/>
-      <x:c r="D27" s="23" t="s"/>
-      <x:c r="E27" s="23" t="s"/>
-      <x:c r="F27" s="24" t="s">
-        <x:v>97</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="25" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C28" s="26" t="s"/>
-      <x:c r="D28" s="26" t="s"/>
-      <x:c r="E28" s="26" t="s"/>
-      <x:c r="F28" s="27" t="n">
-        <x:v>2</x:v>
+    <x:row r="28" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B28" s="22" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C28" s="23" t="s"/>
+      <x:c r="D28" s="23" t="s"/>
+      <x:c r="E28" s="23" t="s"/>
+      <x:c r="F28" s="24" t="s">
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="18" customHeight="1">
       <x:c r="B29" s="25" t="s">
-        <x:v>27</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C29" s="26" t="s"/>
       <x:c r="D29" s="26" t="s"/>
       <x:c r="E29" s="26" t="s"/>
       <x:c r="F29" s="27" t="n">
-        <x:v>8</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="18" customHeight="1">
       <x:c r="B30" s="25" t="s">
-        <x:v>68</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C30" s="26" t="s"/>
       <x:c r="D30" s="26" t="s"/>
       <x:c r="E30" s="26" t="s"/>
       <x:c r="F30" s="27" t="n">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B31" s="25" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="C31" s="26" t="s"/>
+      <x:c r="D31" s="26" t="s"/>
+      <x:c r="E31" s="26" t="s"/>
+      <x:c r="F31" s="27" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B31" s="28" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="C31" s="29" t="s"/>
-      <x:c r="D31" s="29" t="s"/>
-      <x:c r="E31" s="29" t="s"/>
-      <x:c r="F31" s="30" t="n">
-        <x:v>16</x:v>
+    <x:row r="32" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B32" s="28" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C32" s="29" t="s"/>
+      <x:c r="D32" s="29" t="s"/>
+      <x:c r="E32" s="29" t="s"/>
+      <x:c r="F32" s="30" t="n">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2844,12 +2893,12 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B26:F26"/>
-    <x:mergeCell ref="B27:E27"/>
+    <x:mergeCell ref="B27:F27"/>
     <x:mergeCell ref="B28:E28"/>
     <x:mergeCell ref="B29:E29"/>
     <x:mergeCell ref="B30:E30"/>
     <x:mergeCell ref="B31:E31"/>
+    <x:mergeCell ref="B32:E32"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-JUNETTE-PONTILAR-evaluator-cache-serviceTracking-JUNETTE-PONTILAR-X-202501-202612.xlsx
+++ b/reports/service-tracking-report-JUNETTE-PONTILAR-evaluator-cache-serviceTracking-JUNETTE-PONTILAR-X-202501-202612.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="103">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="108">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -126,6 +126,18 @@
     <x:t>1518271 A</x:t>
   </x:si>
   <x:si>
+    <x:t>P-3 NATIONAL HIGHWAY, POBLACION, Alubijid, Misamis Oriental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18-REDP-CAG-01362</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1444-814</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518210 A</x:t>
+  </x:si>
+  <x:si>
     <x:t>NADAL BDLG NATIONAL HIGHWAY, BARANGAY 3, Gingoog City, Misamis Oriental</x:t>
   </x:si>
   <x:si>
@@ -138,18 +150,6 @@
     <x:t>1518230 A</x:t>
   </x:si>
   <x:si>
-    <x:t>P-3 NATIONAL HIGHWAY, POBLACION, Alubijid, Misamis Oriental</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18-REDP-CAG-01362</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1444-814</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1518210 A</x:t>
-  </x:si>
-  <x:si>
     <x:t>EMCOR INCORPORATED</x:t>
   </x:si>
   <x:si>
@@ -241,6 +241,21 @@
   </x:si>
   <x:si>
     <x:t>Retailer/Reseller Permit (RENEWAL)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AJT. GADGETS SHOP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>E-1 G/F AJT Building DOLORES st. CORRALES AVE, Nazareth, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROX-MRR-24-11-525</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1440-123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518280 A</x:t>
   </x:si>
   <x:si>
     <x:t>HO TSAYKI INC</x:t>
@@ -1348,7 +1363,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="H11" s="16">
-        <x:v>46128.2089466088</x:v>
+        <x:v>46132.2785644329</x:v>
       </x:c>
       <x:c r="I11" s="16">
         <x:v>46135</x:v>
@@ -1360,7 +1375,7 @@
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L11" s="18">
-        <x:v>46134.3002672917</x:v>
+        <x:v>46133.1152077083</x:v>
       </x:c>
       <x:c r="M11" s="14" t="s">
         <x:v>21</x:v>
@@ -1386,7 +1401,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="H12" s="16">
-        <x:v>46132.2785644329</x:v>
+        <x:v>46128.2089466088</x:v>
       </x:c>
       <x:c r="I12" s="16">
         <x:v>46135</x:v>
@@ -1398,7 +1413,7 @@
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L12" s="18">
-        <x:v>46133.1152077083</x:v>
+        <x:v>46134.3002672917</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
         <x:v>21</x:v>
@@ -1652,19 +1667,19 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="H19" s="16">
-        <x:v>46134.0293580208</x:v>
+        <x:v>46130.477754919</x:v>
       </x:c>
       <x:c r="I19" s="16">
-        <x:v>46144</x:v>
+        <x:v>45968</x:v>
       </x:c>
       <x:c r="J19" s="15" t="s">
         <x:v>77</x:v>
       </x:c>
       <x:c r="K19" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L19" s="18">
-        <x:v>46139.2265670718</x:v>
+        <x:v>46140.1466972338</x:v>
       </x:c>
       <x:c r="M19" s="14" t="s">
         <x:v>21</x:v>
@@ -1675,34 +1690,34 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C20" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D20" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="E20" s="14" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F20" s="14" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="G20" s="14" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H20" s="16">
-        <x:v>46126.2721295949</x:v>
+        <x:v>46134.0293580208</x:v>
       </x:c>
       <x:c r="I20" s="16">
-        <x:v>46224</x:v>
+        <x:v>46144</x:v>
       </x:c>
       <x:c r="J20" s="15" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="K20" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L20" s="18">
-        <x:v>46128.1955625</x:v>
+        <x:v>46139.2265670718</x:v>
       </x:c>
       <x:c r="M20" s="14" t="s">
         <x:v>21</x:v>
@@ -1713,7 +1728,7 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C21" s="14" t="s">
-        <x:v>82</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D21" s="15" t="s">
         <x:v>29</x:v>
@@ -1728,10 +1743,10 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="H21" s="16">
-        <x:v>46125.335903912</x:v>
+        <x:v>46126.2721295949</x:v>
       </x:c>
       <x:c r="I21" s="16">
-        <x:v>46203</x:v>
+        <x:v>46224</x:v>
       </x:c>
       <x:c r="J21" s="15" t="s">
         <x:v>86</x:v>
@@ -1740,7 +1755,7 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L21" s="18">
-        <x:v>46134.2685065741</x:v>
+        <x:v>46128.1955625</x:v>
       </x:c>
       <x:c r="M21" s="14" t="s">
         <x:v>21</x:v>
@@ -1766,10 +1781,10 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="H22" s="16">
-        <x:v>46126.2873086111</x:v>
+        <x:v>46125.335903912</x:v>
       </x:c>
       <x:c r="I22" s="16">
-        <x:v>46130</x:v>
+        <x:v>46203</x:v>
       </x:c>
       <x:c r="J22" s="15" t="s">
         <x:v>91</x:v>
@@ -1778,7 +1793,7 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L22" s="18">
-        <x:v>46127.0949605556</x:v>
+        <x:v>46134.2685065741</x:v>
       </x:c>
       <x:c r="M22" s="14" t="s">
         <x:v>21</x:v>
@@ -1789,34 +1804,34 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C23" s="14" t="s">
-        <x:v>67</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D23" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="E23" s="14" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F23" s="14" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="G23" s="14" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H23" s="16">
-        <x:v>46126.3215783912</x:v>
+        <x:v>46126.2873086111</x:v>
       </x:c>
       <x:c r="I23" s="16">
-        <x:v>46198</x:v>
+        <x:v>46130</x:v>
       </x:c>
       <x:c r="J23" s="15" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K23" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L23" s="18">
-        <x:v>46128.1824279398</x:v>
+        <x:v>46127.0949605556</x:v>
       </x:c>
       <x:c r="M23" s="14" t="s">
         <x:v>21</x:v>
@@ -1833,100 +1848,137 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="E24" s="14" t="s">
-        <x:v>68</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F24" s="14" t="s">
-        <x:v>96</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="G24" s="14" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="H24" s="16">
-        <x:v>46126.3072273495</x:v>
+        <x:v>46126.3215783912</x:v>
       </x:c>
       <x:c r="I24" s="16">
-        <x:v>46189</x:v>
+        <x:v>46198</x:v>
       </x:c>
       <x:c r="J24" s="15" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="K24" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L24" s="18">
-        <x:v>46128.1930397685</x:v>
+        <x:v>46128.1824279398</x:v>
       </x:c>
       <x:c r="M24" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="25" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B25" s="14" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="C25" s="14" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D25" s="15" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E25" s="14" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="F25" s="14" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="G25" s="14" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="H25" s="16">
+        <x:v>46126.3072273495</x:v>
+      </x:c>
+      <x:c r="I25" s="16">
+        <x:v>46189</x:v>
+      </x:c>
+      <x:c r="J25" s="15" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="K25" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L25" s="18">
+        <x:v>46128.1930397685</x:v>
+      </x:c>
+      <x:c r="M25" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="27" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B27" s="19" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C27" s="20" t="s"/>
-      <x:c r="D27" s="20" t="s"/>
-      <x:c r="E27" s="21" t="s"/>
-      <x:c r="F27" s="21" t="s"/>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B28" s="22" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="C28" s="23" t="s"/>
-      <x:c r="D28" s="23" t="s"/>
-      <x:c r="E28" s="23" t="s"/>
-      <x:c r="F28" s="24" t="s">
-        <x:v>101</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="25" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C29" s="26" t="s"/>
-      <x:c r="D29" s="26" t="s"/>
-      <x:c r="E29" s="26" t="s"/>
-      <x:c r="F29" s="27" t="n">
-        <x:v>2</x:v>
+    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="28" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B28" s="19" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C28" s="20" t="s"/>
+      <x:c r="D28" s="20" t="s"/>
+      <x:c r="E28" s="21" t="s"/>
+      <x:c r="F28" s="21" t="s"/>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B29" s="22" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C29" s="23" t="s"/>
+      <x:c r="D29" s="23" t="s"/>
+      <x:c r="E29" s="23" t="s"/>
+      <x:c r="F29" s="24" t="s">
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="18" customHeight="1">
       <x:c r="B30" s="25" t="s">
-        <x:v>27</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C30" s="26" t="s"/>
       <x:c r="D30" s="26" t="s"/>
       <x:c r="E30" s="26" t="s"/>
       <x:c r="F30" s="27" t="n">
-        <x:v>9</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="18" customHeight="1">
       <x:c r="B31" s="25" t="s">
-        <x:v>72</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C31" s="26" t="s"/>
       <x:c r="D31" s="26" t="s"/>
       <x:c r="E31" s="26" t="s"/>
       <x:c r="F31" s="27" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B32" s="28" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="C32" s="29" t="s"/>
-      <x:c r="D32" s="29" t="s"/>
-      <x:c r="E32" s="29" t="s"/>
-      <x:c r="F32" s="30" t="n">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B32" s="25" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="C32" s="26" t="s"/>
+      <x:c r="D32" s="26" t="s"/>
+      <x:c r="E32" s="26" t="s"/>
+      <x:c r="F32" s="27" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B33" s="28" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="C33" s="29" t="s"/>
+      <x:c r="D33" s="29" t="s"/>
+      <x:c r="E33" s="29" t="s"/>
+      <x:c r="F33" s="30" t="n">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
     <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2893,12 +2945,12 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B27:F27"/>
-    <x:mergeCell ref="B28:E28"/>
+    <x:mergeCell ref="B28:F28"/>
     <x:mergeCell ref="B29:E29"/>
     <x:mergeCell ref="B30:E30"/>
     <x:mergeCell ref="B31:E31"/>
     <x:mergeCell ref="B32:E32"/>
+    <x:mergeCell ref="B33:E33"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-JUNETTE-PONTILAR-evaluator-cache-serviceTracking-JUNETTE-PONTILAR-X-202501-202612.xlsx
+++ b/reports/service-tracking-report-JUNETTE-PONTILAR-evaluator-cache-serviceTracking-JUNETTE-PONTILAR-X-202501-202612.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="108">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -66,6 +66,198 @@
     <x:t>BY</x:t>
   </x:si>
   <x:si>
+    <x:t>Dealer Permit (RENEWAL)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOLIDMARK WEST, INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Robinson's Place, Bagontaas, City Of Valencia, Bukidnon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROX-MRR-24-04-516</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1421-158</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518169</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CHERYL MAY DELOSO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Retailer/Reseller Permit (RENEWAL)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TECHNOMART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>385 Jr Borja St. Aguinaldo, 32, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROX - MRR-10 - 04 - 326</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1429-808</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518180</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNIPACE CORPORATION</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORTICH STREET, Barangay 04, City Of Malaybalay (Capital), Bukidnon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROX-MRR-13-06-152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1433-178</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518188</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14-REDP-CAG-01347</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1432-214</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518189</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROX-MRR-10-06-128</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1431-363</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518190</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTERPACE CORPORATION</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14-REDP-CAG-01346</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1430-046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518191</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROX-MRR-10-07-135</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1428-833</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMCOR INCORPORATED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JVR BLDG J.R BORJA ST., BARANGAY 32, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">18-REDP-CAG-01365 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1434-610</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518195</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMCOR INC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RIZAL AVENUE, 50TH DISTRICT, Ozamis City, Misamis Occidental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18-REDP-CAG-01362</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1444-814</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518210 A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMCOR, INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hannah Shangrila Bldg. Zone 1B, Iponan, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19-REDP-CAG-01364</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1448-935</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518223 A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOLIDMARK WEST, INC. - ROBINSONS VALENCIA SES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROX-MRR-18-12-410</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1424-309</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518227 A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18-REDP-CAG-01361</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1436-764</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518230 A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORO GADGETS INC. (GRAPHIC GADGET STORES)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3E-1 THIRD LEVEL GAISANO PUERTO, PUERTO, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROX-MP-17-04-174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1446-993</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518243 A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HO TSAYKI INC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T-29 &amp; T-30 citymall bulua, Bulua, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROX-MRR-19-05-425</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1449-395</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518265 A</x:t>
+  </x:si>
+  <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
   </x:si>
   <x:si>
@@ -75,9 +267,6 @@
     <x:t>NEW</x:t>
   </x:si>
   <x:si>
-    <x:t>GAISANO TUBOD,PABLACION,TUBOD LANAO DEL NORTE, POBLACION, Tubod (Capital), Lanao Del Norte</x:t>
-  </x:si>
-  <x:si>
     <x:t>MPDP-ROX-08615-26</x:t>
   </x:si>
   <x:si>
@@ -87,9 +276,6 @@
     <x:t>1518266 A</x:t>
   </x:si>
   <x:si>
-    <x:t>CHERYL MAY DELOSO</x:t>
-  </x:si>
-  <x:si>
     <x:t>LAPTAP ENTERPRISES, INC.</x:t>
   </x:si>
   <x:si>
@@ -105,18 +291,6 @@
     <x:t>1518270 A</x:t>
   </x:si>
   <x:si>
-    <x:t>Dealer Permit (RENEWAL)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMCOR INC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RIZAL AVENUE, 50TH DISTRICT, Ozamis City, Misamis Occidental</x:t>
-  </x:si>
-  <x:si>
     <x:t>18-REDP-CAG-01370</x:t>
   </x:si>
   <x:si>
@@ -126,123 +300,6 @@
     <x:t>1518271 A</x:t>
   </x:si>
   <x:si>
-    <x:t>P-3 NATIONAL HIGHWAY, POBLACION, Alubijid, Misamis Oriental</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18-REDP-CAG-01362</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1444-814</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1518210 A</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NADAL BDLG NATIONAL HIGHWAY, BARANGAY 3, Gingoog City, Misamis Oriental</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18-REDP-CAG-01361</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1436-764</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1518230 A</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMCOR INCORPORATED</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JVR BLDG J.R BORJA ST., BARANGAY 32, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">18-REDP-CAG-01365 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1434-610</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1518195</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMCOR, INC.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hannah Shangrila Bldg. Zone 1B, Iponan, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19-REDP-CAG-01364</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1448-935</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1518223 A</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTERPACE CORPORATION</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WEST WING LKKS CENTER, Barangay LAPASAN, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14-REDP-CAG-01346</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1430-046</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1518191</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORO GADGETS INC. (GRAPHIC GADGET STORES)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3E-1 THIRD LEVEL GAISANO PUERTO, PUERTO, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROX-MP-17-04-174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1446-993</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1518243 A</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOLIDMARK WEST, INC.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MVVL3 K1 3RD FLOOR GAISANO CITY, Poblacion, City Of Valencia, Bukidnon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROX-MRR-24-04-516</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-3-2026-1421-158</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1518169</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNIPACE CORPORATION</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CM RECTO AVE., CORRALES EXTN.,, Barangay 26, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14-REDP-CAG-01347</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1432-214</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1518189</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Retailer/Reseller Permit (RENEWAL)</x:t>
-  </x:si>
-  <x:si>
     <x:t>AJT. GADGETS SHOP</x:t>
   </x:si>
   <x:si>
@@ -256,84 +313,6 @@
   </x:si>
   <x:si>
     <x:t>1518280 A</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HO TSAYKI INC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>T-29 &amp; T-30 citymall bulua, Bulua, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROX-MRR-19-05-425</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1449-395</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1518265 A</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WEST WING LKKS CENTER, Barangay 31, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROX-MRR-10-07-135</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1428-833</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1518192</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOLIDMARK WEST, INC. - ROBINSONS VALENCIA SES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Robinson's Place, Bagontaas, City Of Valencia, Bukidnon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROX-MRR-18-12-410</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1424-309</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1518227 A</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TECHNOMART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>385 Jr Borja St. Aguinaldo, 32, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROX - MRR-10 - 04 - 326</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1429-808</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1518180</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORTICH STREET, Barangay 04, City Of Malaybalay (Capital), Bukidnon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROX-MRR-13-06-152</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1433-178</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1518188</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROX-MRR-10-06-128</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1431-363</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1518190</x:t>
   </x:si>
   <x:si>
     <x:t>SUMMARY</x:t>
@@ -1249,19 +1228,19 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="H8" s="16">
-        <x:v>46132.313701713</x:v>
+        <x:v>46112.0874409838</x:v>
       </x:c>
       <x:c r="I8" s="16">
-        <x:v>46132.3137205208</x:v>
+        <x:v>46134</x:v>
       </x:c>
       <x:c r="J8" s="15" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="K8" s="17" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L8" s="18">
-        <x:v>46139.230364294</x:v>
+        <x:v>46125.1598529398</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
@@ -1269,37 +1248,37 @@
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D9" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H9" s="16">
-        <x:v>46129.4086055787</x:v>
+        <x:v>46126.2873086111</x:v>
       </x:c>
       <x:c r="I9" s="16">
-        <x:v>46129.4086256481</x:v>
+        <x:v>46130</x:v>
       </x:c>
       <x:c r="J9" s="15" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="K9" s="17" t="n">
-        <x:v>2130</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L9" s="18">
-        <x:v>46139.3272522222</x:v>
+        <x:v>46127.0949605556</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
@@ -1307,37 +1286,37 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C10" s="14" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="D10" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E10" s="14" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="F10" s="14" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="s">
+      <x:c r="H10" s="16">
+        <x:v>46126.3215783912</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
+        <x:v>46198</x:v>
+      </x:c>
+      <x:c r="J10" s="15" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="H10" s="16">
-        <x:v>46137.0314533796</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>46149</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="s">
-        <x:v>33</x:v>
-      </x:c>
       <x:c r="K10" s="17" t="n">
-        <x:v>1950</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L10" s="18">
-        <x:v>46139.3366940046</x:v>
+        <x:v>46128.1824279398</x:v>
       </x:c>
       <x:c r="M10" s="14" t="s">
         <x:v>21</x:v>
@@ -1345,37 +1324,37 @@
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
-        <x:v>27</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C11" s="14" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="D11" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E11" s="14" t="s">
+      <x:c r="F11" s="14" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="F11" s="14" t="s">
+      <x:c r="H11" s="16">
+        <x:v>46126.3116678125</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
+        <x:v>46196</x:v>
+      </x:c>
+      <x:c r="J11" s="15" t="s">
         <x:v>35</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>46132.2785644329</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>46135</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="s">
-        <x:v>37</x:v>
       </x:c>
       <x:c r="K11" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L11" s="18">
-        <x:v>46133.1152077083</x:v>
+        <x:v>46128.191368669</x:v>
       </x:c>
       <x:c r="M11" s="14" t="s">
         <x:v>21</x:v>
@@ -1383,37 +1362,37 @@
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="14" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C12" s="14" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="D12" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E12" s="14" t="s">
+      <x:c r="F12" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
+        <x:v>46126.3072273495</x:v>
+      </x:c>
+      <x:c r="I12" s="16">
+        <x:v>46189</x:v>
+      </x:c>
+      <x:c r="J12" s="15" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="F12" s="14" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="H12" s="16">
-        <x:v>46128.2089466088</x:v>
-      </x:c>
-      <x:c r="I12" s="16">
-        <x:v>46135</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="s">
-        <x:v>41</x:v>
-      </x:c>
       <x:c r="K12" s="17" t="n">
-        <x:v>1950</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L12" s="18">
-        <x:v>46134.3002672917</x:v>
+        <x:v>46128.1930397685</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
         <x:v>21</x:v>
@@ -1421,37 +1400,37 @@
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="14" t="s">
-        <x:v>27</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C13" s="14" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
+        <x:v>46126.2900560185</x:v>
+      </x:c>
+      <x:c r="I13" s="16">
+        <x:v>46162</x:v>
+      </x:c>
+      <x:c r="J13" s="15" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="D13" s="15" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="F13" s="14" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="G13" s="14" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="H13" s="16">
-        <x:v>46128.1699027199</x:v>
-      </x:c>
-      <x:c r="I13" s="16">
-        <x:v>46136</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="s">
-        <x:v>46</x:v>
       </x:c>
       <x:c r="K13" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L13" s="18">
-        <x:v>46128.349008206</x:v>
+        <x:v>46128.194732662</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
         <x:v>21</x:v>
@@ -1459,37 +1438,37 @@
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="14" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C14" s="14" t="s">
-        <x:v>47</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D14" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E14" s="14" t="s">
-        <x:v>48</x:v>
-      </x:c>
       <x:c r="F14" s="14" t="s">
-        <x:v>49</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G14" s="14" t="s">
-        <x:v>50</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H14" s="16">
-        <x:v>46133.2374101505</x:v>
+        <x:v>46126.2721295949</x:v>
       </x:c>
       <x:c r="I14" s="16">
-        <x:v>46135</x:v>
+        <x:v>46224</x:v>
       </x:c>
       <x:c r="J14" s="15" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="K14" s="17" t="n">
-        <x:v>1950</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L14" s="18">
-        <x:v>46134.0815209838</x:v>
+        <x:v>46128.1955625</x:v>
       </x:c>
       <x:c r="M14" s="14" t="s">
         <x:v>21</x:v>
@@ -1497,37 +1476,37 @@
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="14" t="s">
-        <x:v>27</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C15" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D15" s="15" t="s">
-        <x:v>29</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E15" s="14" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F15" s="14" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G15" s="14" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H15" s="16">
-        <x:v>46126.2900560185</x:v>
+        <x:v>46128.1699027199</x:v>
       </x:c>
       <x:c r="I15" s="16">
-        <x:v>46162</x:v>
+        <x:v>46136</x:v>
       </x:c>
       <x:c r="J15" s="15" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="K15" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L15" s="18">
-        <x:v>46128.194732662</x:v>
+        <x:v>46128.349008206</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
         <x:v>21</x:v>
@@ -1535,37 +1514,37 @@
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="14" t="s">
-        <x:v>27</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C16" s="14" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D16" s="15" t="s">
-        <x:v>29</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E16" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F16" s="14" t="s">
-        <x:v>59</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G16" s="14" t="s">
-        <x:v>60</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H16" s="16">
-        <x:v>46132.3880687384</x:v>
+        <x:v>46132.2785644329</x:v>
       </x:c>
       <x:c r="I16" s="16">
-        <x:v>46138</x:v>
+        <x:v>46135</x:v>
       </x:c>
       <x:c r="J16" s="15" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="K16" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L16" s="18">
-        <x:v>46135.1691307292</x:v>
+        <x:v>46133.1152077083</x:v>
       </x:c>
       <x:c r="M16" s="14" t="s">
         <x:v>21</x:v>
@@ -1573,37 +1552,37 @@
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="14" t="s">
-        <x:v>27</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C17" s="14" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D17" s="15" t="s">
-        <x:v>29</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E17" s="14" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F17" s="14" t="s">
-        <x:v>64</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G17" s="14" t="s">
-        <x:v>65</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H17" s="16">
-        <x:v>46112.0874409838</x:v>
+        <x:v>46133.2374101505</x:v>
       </x:c>
       <x:c r="I17" s="16">
-        <x:v>46134</x:v>
+        <x:v>46135</x:v>
       </x:c>
       <x:c r="J17" s="15" t="s">
-        <x:v>66</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="K17" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L17" s="18">
-        <x:v>46125.1598529398</x:v>
+        <x:v>46134.0815209838</x:v>
       </x:c>
       <x:c r="M17" s="14" t="s">
         <x:v>21</x:v>
@@ -1611,37 +1590,37 @@
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="14" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C18" s="14" t="s">
-        <x:v>67</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D18" s="15" t="s">
-        <x:v>29</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E18" s="14" t="s">
-        <x:v>68</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F18" s="14" t="s">
-        <x:v>69</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G18" s="14" t="s">
-        <x:v>70</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H18" s="16">
-        <x:v>46126.3116678125</x:v>
+        <x:v>46125.335903912</x:v>
       </x:c>
       <x:c r="I18" s="16">
-        <x:v>46196</x:v>
+        <x:v>46203</x:v>
       </x:c>
       <x:c r="J18" s="15" t="s">
-        <x:v>71</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="K18" s="17" t="n">
-        <x:v>1950</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L18" s="18">
-        <x:v>46128.191368669</x:v>
+        <x:v>46134.2685065741</x:v>
       </x:c>
       <x:c r="M18" s="14" t="s">
         <x:v>21</x:v>
@@ -1649,37 +1628,37 @@
     </x:row>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
       <x:c r="B19" s="14" t="s">
-        <x:v>72</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C19" s="14" t="s">
-        <x:v>73</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D19" s="15" t="s">
-        <x:v>29</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E19" s="14" t="s">
-        <x:v>74</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F19" s="14" t="s">
-        <x:v>75</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="G19" s="14" t="s">
-        <x:v>76</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="H19" s="16">
-        <x:v>46130.477754919</x:v>
+        <x:v>46128.2089466088</x:v>
       </x:c>
       <x:c r="I19" s="16">
-        <x:v>45968</x:v>
+        <x:v>46135</x:v>
       </x:c>
       <x:c r="J19" s="15" t="s">
-        <x:v>77</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="K19" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L19" s="18">
-        <x:v>46140.1466972338</x:v>
+        <x:v>46134.3002672917</x:v>
       </x:c>
       <x:c r="M19" s="14" t="s">
         <x:v>21</x:v>
@@ -1687,37 +1666,37 @@
     </x:row>
     <x:row r="20" spans="1:28" ht="30" customHeight="1">
       <x:c r="B20" s="14" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C20" s="14" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D20" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E20" s="14" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="G20" s="14" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="H20" s="16">
+        <x:v>46132.3880687384</x:v>
+      </x:c>
+      <x:c r="I20" s="16">
+        <x:v>46138</x:v>
+      </x:c>
+      <x:c r="J20" s="15" t="s">
         <x:v>72</x:v>
-      </x:c>
-      <x:c r="C20" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="D20" s="15" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E20" s="14" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="F20" s="14" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="G20" s="14" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="H20" s="16">
-        <x:v>46134.0293580208</x:v>
-      </x:c>
-      <x:c r="I20" s="16">
-        <x:v>46144</x:v>
-      </x:c>
-      <x:c r="J20" s="15" t="s">
-        <x:v>82</x:v>
       </x:c>
       <x:c r="K20" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L20" s="18">
-        <x:v>46139.2265670718</x:v>
+        <x:v>46135.1691307292</x:v>
       </x:c>
       <x:c r="M20" s="14" t="s">
         <x:v>21</x:v>
@@ -1725,37 +1704,37 @@
     </x:row>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
       <x:c r="B21" s="14" t="s">
-        <x:v>72</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C21" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D21" s="15" t="s">
-        <x:v>29</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E21" s="14" t="s">
-        <x:v>83</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F21" s="14" t="s">
-        <x:v>84</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="G21" s="14" t="s">
-        <x:v>85</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="H21" s="16">
-        <x:v>46126.2721295949</x:v>
+        <x:v>46134.0293580208</x:v>
       </x:c>
       <x:c r="I21" s="16">
-        <x:v>46224</x:v>
+        <x:v>46144</x:v>
       </x:c>
       <x:c r="J21" s="15" t="s">
-        <x:v>86</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="K21" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L21" s="18">
-        <x:v>46128.1955625</x:v>
+        <x:v>46139.2265670718</x:v>
       </x:c>
       <x:c r="M21" s="14" t="s">
         <x:v>21</x:v>
@@ -1763,37 +1742,37 @@
     </x:row>
     <x:row r="22" spans="1:28" ht="30" customHeight="1">
       <x:c r="B22" s="14" t="s">
-        <x:v>72</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C22" s="14" t="s">
-        <x:v>87</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D22" s="15" t="s">
-        <x:v>29</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E22" s="14" t="s">
-        <x:v>88</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F22" s="14" t="s">
-        <x:v>89</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="G22" s="14" t="s">
-        <x:v>90</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="H22" s="16">
-        <x:v>46125.335903912</x:v>
+        <x:v>46132.313701713</x:v>
       </x:c>
       <x:c r="I22" s="16">
-        <x:v>46203</x:v>
+        <x:v>46132.3137205208</x:v>
       </x:c>
       <x:c r="J22" s="15" t="s">
-        <x:v>91</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="K22" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L22" s="18">
-        <x:v>46134.2685065741</x:v>
+        <x:v>46139.230364294</x:v>
       </x:c>
       <x:c r="M22" s="14" t="s">
         <x:v>21</x:v>
@@ -1801,37 +1780,37 @@
     </x:row>
     <x:row r="23" spans="1:28" ht="30" customHeight="1">
       <x:c r="B23" s="14" t="s">
-        <x:v>72</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C23" s="14" t="s">
-        <x:v>92</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D23" s="15" t="s">
-        <x:v>29</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E23" s="14" t="s">
-        <x:v>93</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F23" s="14" t="s">
-        <x:v>94</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G23" s="14" t="s">
-        <x:v>95</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="H23" s="16">
-        <x:v>46126.2873086111</x:v>
+        <x:v>46129.4086055787</x:v>
       </x:c>
       <x:c r="I23" s="16">
-        <x:v>46130</x:v>
+        <x:v>46129.4086256481</x:v>
       </x:c>
       <x:c r="J23" s="15" t="s">
-        <x:v>96</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="K23" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>2130</x:v>
       </x:c>
       <x:c r="L23" s="18">
-        <x:v>46127.0949605556</x:v>
+        <x:v>46139.3272522222</x:v>
       </x:c>
       <x:c r="M23" s="14" t="s">
         <x:v>21</x:v>
@@ -1839,37 +1818,37 @@
     </x:row>
     <x:row r="24" spans="1:28" ht="30" customHeight="1">
       <x:c r="B24" s="14" t="s">
-        <x:v>72</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C24" s="14" t="s">
-        <x:v>67</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D24" s="15" t="s">
-        <x:v>29</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E24" s="14" t="s">
-        <x:v>97</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F24" s="14" t="s">
-        <x:v>98</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="G24" s="14" t="s">
-        <x:v>99</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H24" s="16">
-        <x:v>46126.3215783912</x:v>
+        <x:v>46137.0314533796</x:v>
       </x:c>
       <x:c r="I24" s="16">
-        <x:v>46198</x:v>
+        <x:v>46149</x:v>
       </x:c>
       <x:c r="J24" s="15" t="s">
-        <x:v>100</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="K24" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L24" s="18">
-        <x:v>46128.1824279398</x:v>
+        <x:v>46139.3366940046</x:v>
       </x:c>
       <x:c r="M24" s="14" t="s">
         <x:v>21</x:v>
@@ -1877,37 +1856,37 @@
     </x:row>
     <x:row r="25" spans="1:28" ht="30" customHeight="1">
       <x:c r="B25" s="14" t="s">
-        <x:v>72</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C25" s="14" t="s">
-        <x:v>67</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D25" s="15" t="s">
-        <x:v>29</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E25" s="14" t="s">
-        <x:v>68</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F25" s="14" t="s">
-        <x:v>101</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="G25" s="14" t="s">
-        <x:v>102</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H25" s="16">
-        <x:v>46126.3072273495</x:v>
+        <x:v>46130.477754919</x:v>
       </x:c>
       <x:c r="I25" s="16">
-        <x:v>46189</x:v>
+        <x:v>45968</x:v>
       </x:c>
       <x:c r="J25" s="15" t="s">
-        <x:v>103</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K25" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L25" s="18">
-        <x:v>46128.1930397685</x:v>
+        <x:v>46140.1466972338</x:v>
       </x:c>
       <x:c r="M25" s="14" t="s">
         <x:v>21</x:v>
@@ -1917,7 +1896,7 @@
     <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="28" spans="1:28" ht="30" customHeight="1">
       <x:c r="B28" s="19" t="s">
-        <x:v>104</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C28" s="20" t="s"/>
       <x:c r="D28" s="20" t="s"/>
@@ -1926,18 +1905,18 @@
     </x:row>
     <x:row r="29" spans="1:28" ht="22" customHeight="1">
       <x:c r="B29" s="22" t="s">
-        <x:v>105</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C29" s="23" t="s"/>
       <x:c r="D29" s="23" t="s"/>
       <x:c r="E29" s="23" t="s"/>
       <x:c r="F29" s="24" t="s">
-        <x:v>106</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="18" customHeight="1">
       <x:c r="B30" s="25" t="s">
-        <x:v>14</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C30" s="26" t="s"/>
       <x:c r="D30" s="26" t="s"/>
@@ -1948,7 +1927,7 @@
     </x:row>
     <x:row r="31" spans="1:28" ht="18" customHeight="1">
       <x:c r="B31" s="25" t="s">
-        <x:v>27</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C31" s="26" t="s"/>
       <x:c r="D31" s="26" t="s"/>
@@ -1959,7 +1938,7 @@
     </x:row>
     <x:row r="32" spans="1:28" ht="18" customHeight="1">
       <x:c r="B32" s="25" t="s">
-        <x:v>72</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C32" s="26" t="s"/>
       <x:c r="D32" s="26" t="s"/>
@@ -1970,7 +1949,7 @@
     </x:row>
     <x:row r="33" spans="1:28" ht="28" customHeight="1">
       <x:c r="B33" s="28" t="s">
-        <x:v>107</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C33" s="29" t="s"/>
       <x:c r="D33" s="29" t="s"/>
